--- a/Task-1-TestCase-by(sanjay srinivas T).xlsx
+++ b/Task-1-TestCase-by(sanjay srinivas T).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3fc2e1139c06ea87/Desktop/Tichi-assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7ABD9D2-253E-47D2-A19D-59E8DFE55EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{E7ABD9D2-253E-47D2-A19D-59E8DFE55EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E0C8BB7-4AEC-48E4-9CD5-2BCEA5989602}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{1010C715-7696-41A7-9CF7-2C5ABBBA349D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="323">
   <si>
     <t>TEST CASE REPORT</t>
   </si>
@@ -997,13 +997,19 @@
   </si>
   <si>
     <t>sign in page is redirected to home page of website successfully</t>
+  </si>
+  <si>
+    <t>TESTED BY: SANJAY SRINIVAS T</t>
+  </si>
+  <si>
+    <t>PROJECT DETAILS ABOVE 9TH ROW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1060,8 +1066,14 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1147,6 +1159,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -1288,7 +1306,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="15">
+  <cellStyleXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1304,8 +1322,9 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1402,12 +1421,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="15" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1429,10 +1446,10 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1472,8 +1489,9 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="14" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="15">
+  <cellStyles count="16">
     <cellStyle name="20% - Accent1" xfId="3" builtinId="30"/>
     <cellStyle name="20% - Accent2" xfId="5" builtinId="34"/>
     <cellStyle name="20% - Accent3" xfId="7" builtinId="38"/>
@@ -1482,6 +1500,7 @@
     <cellStyle name="20% - Accent6" xfId="12" builtinId="50"/>
     <cellStyle name="40% - Accent2" xfId="6" builtinId="35"/>
     <cellStyle name="40% - Accent5" xfId="11" builtinId="47"/>
+    <cellStyle name="60% - Accent2" xfId="15" builtinId="36"/>
     <cellStyle name="60% - Accent4" xfId="9" builtinId="44"/>
     <cellStyle name="60% - Accent6" xfId="13" builtinId="52"/>
     <cellStyle name="Accent1" xfId="2" builtinId="29"/>
@@ -1819,116 +1838,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="52"/>
+      <c r="B2" s="54"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="G2" s="52" t="s">
+      <c r="G2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="53" t="s">
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
       <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="57" t="s">
+      <c r="B3" s="54"/>
+      <c r="C3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="57"/>
+      <c r="D3" s="59"/>
       <c r="E3" s="3"/>
-      <c r="G3" s="52" t="s">
+      <c r="G3" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="53" t="s">
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53" t="s">
+      <c r="B4" s="54"/>
+      <c r="C4" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="G4" s="52" t="s">
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="G4" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="54">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="56">
         <v>46029</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="53" t="s">
+      <c r="B5" s="57"/>
+      <c r="C5" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="G5" s="55" t="s">
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="G5" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="54">
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="56">
         <v>46060</v>
       </c>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
+      <c r="K5" s="55"/>
+      <c r="L5" s="55"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1944,10 +1963,10 @@
       <c r="D9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="47" t="s">
+      <c r="E9" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="48"/>
+      <c r="F9" s="50"/>
       <c r="G9" s="5" t="s">
         <v>19</v>
       </c>
@@ -1969,18 +1988,18 @@
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A10" s="49"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="51"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="52"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="52"/>
+      <c r="L10" s="53"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13" ht="36" x14ac:dyDescent="0.4">
@@ -1996,10 +2015,10 @@
       <c r="D11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="39"/>
+      <c r="F11" s="41"/>
       <c r="G11" s="7" t="s">
         <v>30</v>
       </c>
@@ -2033,10 +2052,10 @@
       <c r="D12" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="39"/>
+      <c r="F12" s="41"/>
       <c r="G12" s="7" t="s">
         <v>30</v>
       </c>
@@ -2058,18 +2077,18 @@
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A13" s="40"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="42"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
+      <c r="J13" s="43"/>
+      <c r="K13" s="43"/>
+      <c r="L13" s="44"/>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -2085,10 +2104,10 @@
       <c r="D14" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="38" t="s">
+      <c r="E14" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="39"/>
+      <c r="F14" s="41"/>
       <c r="G14" s="7" t="s">
         <v>30</v>
       </c>
@@ -2122,10 +2141,10 @@
       <c r="D15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="39"/>
+      <c r="F15" s="41"/>
       <c r="G15" s="7" t="s">
         <v>30</v>
       </c>
@@ -2159,10 +2178,10 @@
       <c r="D16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="E16" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="F16" s="39"/>
+      <c r="F16" s="41"/>
       <c r="G16" s="7" t="s">
         <v>30</v>
       </c>
@@ -2211,10 +2230,10 @@
       <c r="D18" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="39"/>
+      <c r="F18" s="41"/>
       <c r="G18" s="7" t="s">
         <v>30</v>
       </c>
@@ -2248,10 +2267,10 @@
       <c r="D19" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="39"/>
+      <c r="F19" s="41"/>
       <c r="G19" s="7" t="s">
         <v>66</v>
       </c>
@@ -2285,10 +2304,10 @@
       <c r="D20" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="39"/>
+      <c r="F20" s="41"/>
       <c r="G20" s="7" t="s">
         <v>73</v>
       </c>
@@ -2337,10 +2356,10 @@
       <c r="D22" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="F22" s="39"/>
+      <c r="F22" s="41"/>
       <c r="G22" s="7" t="s">
         <v>30</v>
       </c>
@@ -2374,10 +2393,10 @@
       <c r="D23" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="39"/>
+      <c r="F23" s="41"/>
       <c r="G23" s="7" t="s">
         <v>86</v>
       </c>
@@ -2411,10 +2430,10 @@
       <c r="D24" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="39"/>
+      <c r="F24" s="41"/>
       <c r="G24" s="7" t="s">
         <v>92</v>
       </c>
@@ -2448,10 +2467,10 @@
       <c r="D25" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="39"/>
+      <c r="F25" s="41"/>
       <c r="G25" s="7" t="s">
         <v>98</v>
       </c>
@@ -2485,10 +2504,10 @@
       <c r="D26" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="43" t="s">
+      <c r="E26" s="46" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="39"/>
+      <c r="F26" s="41"/>
       <c r="G26" s="23" t="s">
         <v>107</v>
       </c>
@@ -2522,10 +2541,10 @@
       <c r="D27" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="36" t="s">
+      <c r="E27" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="F27" s="36"/>
+      <c r="F27" s="38"/>
       <c r="G27" s="7" t="s">
         <v>113</v>
       </c>
@@ -2559,10 +2578,10 @@
       <c r="D28" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="E28" s="36" t="s">
+      <c r="E28" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="F28" s="36"/>
+      <c r="F28" s="38"/>
       <c r="G28" s="7" t="s">
         <v>30</v>
       </c>
@@ -2596,10 +2615,10 @@
       <c r="D29" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="36" t="s">
+      <c r="E29" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="F29" s="36"/>
+      <c r="F29" s="38"/>
       <c r="G29" s="7" t="s">
         <v>126</v>
       </c>
@@ -2633,10 +2652,10 @@
       <c r="D30" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="E30" s="44" t="s">
+      <c r="E30" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="F30" s="44"/>
+      <c r="F30" s="45"/>
       <c r="G30" s="25" t="s">
         <v>132</v>
       </c>
@@ -2658,18 +2677,18 @@
       <c r="M30" s="2"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A31" s="40"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="41"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="41"/>
-      <c r="K31" s="41"/>
-      <c r="L31" s="42"/>
+      <c r="A31" s="42"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="44"/>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -2685,10 +2704,10 @@
       <c r="D32" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="E32" s="36" t="s">
+      <c r="E32" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F32" s="36"/>
+      <c r="F32" s="38"/>
       <c r="G32" s="7" t="s">
         <v>30</v>
       </c>
@@ -2722,10 +2741,10 @@
       <c r="D33" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="E33" s="36" t="s">
+      <c r="E33" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F33" s="36"/>
+      <c r="F33" s="38"/>
       <c r="G33" s="7" t="s">
         <v>30</v>
       </c>
@@ -2759,10 +2778,10 @@
       <c r="D34" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E34" s="36" t="s">
+      <c r="E34" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="36"/>
+      <c r="F34" s="38"/>
       <c r="G34" s="7" t="s">
         <v>30</v>
       </c>
@@ -2796,10 +2815,10 @@
       <c r="D35" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E35" s="36" t="s">
+      <c r="E35" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F35" s="36"/>
+      <c r="F35" s="38"/>
       <c r="G35" s="7" t="s">
         <v>30</v>
       </c>
@@ -2833,10 +2852,10 @@
       <c r="D36" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="36" t="s">
+      <c r="E36" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F36" s="36"/>
+      <c r="F36" s="38"/>
       <c r="G36" s="7" t="s">
         <v>30</v>
       </c>
@@ -2870,10 +2889,10 @@
       <c r="D37" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E37" s="36" t="s">
+      <c r="E37" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="F37" s="36"/>
+      <c r="F37" s="38"/>
       <c r="G37" s="7" t="s">
         <v>30</v>
       </c>
@@ -2907,10 +2926,10 @@
       <c r="D38" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E38" s="36" t="s">
+      <c r="E38" s="38" t="s">
         <v>160</v>
       </c>
-      <c r="F38" s="36"/>
+      <c r="F38" s="38"/>
       <c r="G38" s="7" t="s">
         <v>30</v>
       </c>
@@ -2944,10 +2963,10 @@
       <c r="D39" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="E39" s="36" t="s">
+      <c r="E39" s="38" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="36"/>
+      <c r="F39" s="38"/>
       <c r="G39" s="7" t="s">
         <v>126</v>
       </c>
@@ -2981,10 +3000,10 @@
       <c r="D40" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E40" s="36" t="s">
+      <c r="E40" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F40" s="36"/>
+      <c r="F40" s="38"/>
       <c r="G40" s="7" t="s">
         <v>30</v>
       </c>
@@ -3018,10 +3037,10 @@
       <c r="D41" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="E41" s="36" t="s">
+      <c r="E41" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F41" s="36"/>
+      <c r="F41" s="38"/>
       <c r="G41" s="7" t="s">
         <v>30</v>
       </c>
@@ -3043,18 +3062,18 @@
       <c r="M41" s="2"/>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A42" s="40"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="42"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="44"/>
       <c r="M42" s="2"/>
     </row>
     <row r="43" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -3070,10 +3089,10 @@
       <c r="D43" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E43" s="36" t="s">
+      <c r="E43" s="38" t="s">
         <v>183</v>
       </c>
-      <c r="F43" s="36"/>
+      <c r="F43" s="38"/>
       <c r="G43" s="7" t="s">
         <v>184</v>
       </c>
@@ -3107,10 +3126,10 @@
       <c r="D44" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E44" s="36" t="s">
+      <c r="E44" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="F44" s="36"/>
+      <c r="F44" s="38"/>
       <c r="G44" s="7" t="s">
         <v>190</v>
       </c>
@@ -3144,10 +3163,10 @@
       <c r="D45" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E45" s="36" t="s">
+      <c r="E45" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="F45" s="36"/>
+      <c r="F45" s="38"/>
       <c r="G45" s="7" t="s">
         <v>197</v>
       </c>
@@ -3169,18 +3188,18 @@
       <c r="M45" s="2"/>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A46" s="40"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="42"/>
+      <c r="A46" s="42"/>
+      <c r="B46" s="43"/>
+      <c r="C46" s="43"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
+      <c r="G46" s="43"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="44"/>
       <c r="M46" s="2"/>
     </row>
     <row r="47" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -3196,10 +3215,10 @@
       <c r="D47" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E47" s="36" t="s">
+      <c r="E47" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="F47" s="36"/>
+      <c r="F47" s="38"/>
       <c r="G47" s="7" t="s">
         <v>204</v>
       </c>
@@ -3233,10 +3252,10 @@
       <c r="D48" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="E48" s="36" t="s">
+      <c r="E48" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="F48" s="36"/>
+      <c r="F48" s="38"/>
       <c r="G48" s="7" t="s">
         <v>208</v>
       </c>
@@ -3270,10 +3289,10 @@
       <c r="D49" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="E49" s="36" t="s">
+      <c r="E49" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="F49" s="36"/>
+      <c r="F49" s="38"/>
       <c r="G49" s="7" t="s">
         <v>211</v>
       </c>
@@ -3295,18 +3314,18 @@
       <c r="M49" s="2"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A50" s="40"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="42"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="43"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
+      <c r="G50" s="43"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="43"/>
+      <c r="L50" s="44"/>
       <c r="M50" s="2"/>
     </row>
     <row r="51" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -3322,10 +3341,10 @@
       <c r="D51" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E51" s="38" t="s">
+      <c r="E51" s="40" t="s">
         <v>216</v>
       </c>
-      <c r="F51" s="39"/>
+      <c r="F51" s="41"/>
       <c r="G51" s="7" t="s">
         <v>30</v>
       </c>
@@ -3359,10 +3378,10 @@
       <c r="D52" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E52" s="38" t="s">
+      <c r="E52" s="40" t="s">
         <v>221</v>
       </c>
-      <c r="F52" s="39"/>
+      <c r="F52" s="41"/>
       <c r="G52" s="7" t="s">
         <v>30</v>
       </c>
@@ -3396,10 +3415,10 @@
       <c r="D53" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E53" s="38" t="s">
+      <c r="E53" s="40" t="s">
         <v>226</v>
       </c>
-      <c r="F53" s="39"/>
+      <c r="F53" s="41"/>
       <c r="G53" s="7">
         <v>9988776655</v>
       </c>
@@ -3433,10 +3452,10 @@
       <c r="D54" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E54" s="38" t="s">
+      <c r="E54" s="40" t="s">
         <v>231</v>
       </c>
-      <c r="F54" s="39"/>
+      <c r="F54" s="41"/>
       <c r="G54" s="7">
         <v>998877665</v>
       </c>
@@ -3470,10 +3489,10 @@
       <c r="D55" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E55" s="38" t="s">
+      <c r="E55" s="40" t="s">
         <v>236</v>
       </c>
-      <c r="F55" s="39"/>
+      <c r="F55" s="41"/>
       <c r="G55" s="7">
         <v>99887766554</v>
       </c>
@@ -3507,10 +3526,10 @@
       <c r="D56" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E56" s="38" t="s">
+      <c r="E56" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="F56" s="39"/>
+      <c r="F56" s="41"/>
       <c r="G56" s="7" t="s">
         <v>241</v>
       </c>
@@ -3532,18 +3551,18 @@
       <c r="M56" s="2"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A57" s="40"/>
-      <c r="B57" s="41"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="42"/>
+      <c r="A57" s="42"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="43"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="43"/>
+      <c r="H57" s="43"/>
+      <c r="I57" s="43"/>
+      <c r="J57" s="43"/>
+      <c r="K57" s="43"/>
+      <c r="L57" s="44"/>
       <c r="M57" s="2"/>
     </row>
     <row r="58" spans="1:13" ht="90" x14ac:dyDescent="0.4">
@@ -3559,10 +3578,10 @@
       <c r="D58" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E58" s="38" t="s">
+      <c r="E58" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="F58" s="39"/>
+      <c r="F58" s="41"/>
       <c r="G58" s="7" t="s">
         <v>30</v>
       </c>
@@ -3596,10 +3615,10 @@
       <c r="D59" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E59" s="38" t="s">
+      <c r="E59" s="40" t="s">
         <v>252</v>
       </c>
-      <c r="F59" s="39"/>
+      <c r="F59" s="41"/>
       <c r="G59" s="7" t="s">
         <v>253</v>
       </c>
@@ -3633,10 +3652,10 @@
       <c r="D60" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E60" s="38" t="s">
+      <c r="E60" s="40" t="s">
         <v>258</v>
       </c>
-      <c r="F60" s="39"/>
+      <c r="F60" s="41"/>
       <c r="G60" s="7" t="s">
         <v>259</v>
       </c>
@@ -3670,10 +3689,10 @@
       <c r="D61" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E61" s="38" t="s">
+      <c r="E61" s="40" t="s">
         <v>263</v>
       </c>
-      <c r="F61" s="39"/>
+      <c r="F61" s="41"/>
       <c r="G61" s="7" t="s">
         <v>264</v>
       </c>
@@ -3707,10 +3726,10 @@
       <c r="D62" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E62" s="38" t="s">
+      <c r="E62" s="40" t="s">
         <v>269</v>
       </c>
-      <c r="F62" s="39"/>
+      <c r="F62" s="41"/>
       <c r="G62" s="7" t="s">
         <v>270</v>
       </c>
@@ -3732,18 +3751,18 @@
       <c r="M62" s="2"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A63" s="40"/>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="41"/>
-      <c r="G63" s="41"/>
-      <c r="H63" s="41"/>
-      <c r="I63" s="41"/>
-      <c r="J63" s="41"/>
-      <c r="K63" s="41"/>
-      <c r="L63" s="42"/>
+      <c r="A63" s="42"/>
+      <c r="B63" s="43"/>
+      <c r="C63" s="43"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="43"/>
+      <c r="F63" s="43"/>
+      <c r="G63" s="43"/>
+      <c r="H63" s="43"/>
+      <c r="I63" s="43"/>
+      <c r="J63" s="43"/>
+      <c r="K63" s="43"/>
+      <c r="L63" s="44"/>
       <c r="M63" s="2"/>
     </row>
     <row r="64" spans="1:13" ht="90" x14ac:dyDescent="0.4">
@@ -3759,10 +3778,10 @@
       <c r="D64" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E64" s="38" t="s">
+      <c r="E64" s="40" t="s">
         <v>276</v>
       </c>
-      <c r="F64" s="39"/>
+      <c r="F64" s="41"/>
       <c r="G64" s="7" t="s">
         <v>30</v>
       </c>
@@ -3796,10 +3815,10 @@
       <c r="D65" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E65" s="38" t="s">
+      <c r="E65" s="40" t="s">
         <v>280</v>
       </c>
-      <c r="F65" s="39"/>
+      <c r="F65" s="41"/>
       <c r="G65" s="7" t="s">
         <v>281</v>
       </c>
@@ -3833,10 +3852,10 @@
       <c r="D66" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E66" s="38" t="s">
+      <c r="E66" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="F66" s="39"/>
+      <c r="F66" s="41"/>
       <c r="G66" s="7" t="s">
         <v>281</v>
       </c>
@@ -3870,10 +3889,10 @@
       <c r="D67" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E67" s="38" t="s">
+      <c r="E67" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="F67" s="39"/>
+      <c r="F67" s="41"/>
       <c r="G67" s="7" t="s">
         <v>281</v>
       </c>
@@ -3907,10 +3926,10 @@
       <c r="D68" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E68" s="38" t="s">
+      <c r="E68" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="F68" s="39"/>
+      <c r="F68" s="41"/>
       <c r="G68" s="7" t="s">
         <v>296</v>
       </c>
@@ -3932,18 +3951,18 @@
       <c r="M68" s="2"/>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A69" s="40"/>
-      <c r="B69" s="41"/>
-      <c r="C69" s="41"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="41"/>
-      <c r="F69" s="41"/>
-      <c r="G69" s="41"/>
-      <c r="H69" s="41"/>
-      <c r="I69" s="41"/>
-      <c r="J69" s="41"/>
-      <c r="K69" s="41"/>
-      <c r="L69" s="42"/>
+      <c r="A69" s="42"/>
+      <c r="B69" s="43"/>
+      <c r="C69" s="43"/>
+      <c r="D69" s="43"/>
+      <c r="E69" s="43"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="43"/>
+      <c r="H69" s="43"/>
+      <c r="I69" s="43"/>
+      <c r="J69" s="43"/>
+      <c r="K69" s="43"/>
+      <c r="L69" s="44"/>
       <c r="M69" s="2"/>
     </row>
     <row r="70" spans="1:13" ht="72" x14ac:dyDescent="0.4">
@@ -3959,10 +3978,10 @@
       <c r="D70" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E70" s="38" t="s">
+      <c r="E70" s="40" t="s">
         <v>302</v>
       </c>
-      <c r="F70" s="39"/>
+      <c r="F70" s="41"/>
       <c r="G70" s="7" t="s">
         <v>303</v>
       </c>
@@ -3996,10 +4015,10 @@
       <c r="D71" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E71" s="38" t="s">
+      <c r="E71" s="40" t="s">
         <v>308</v>
       </c>
-      <c r="F71" s="39"/>
+      <c r="F71" s="41"/>
       <c r="G71" s="7" t="s">
         <v>309</v>
       </c>
@@ -4033,10 +4052,10 @@
       <c r="D72" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E72" s="38" t="s">
+      <c r="E72" s="40" t="s">
         <v>314</v>
       </c>
-      <c r="F72" s="39"/>
+      <c r="F72" s="41"/>
       <c r="G72" s="7" t="s">
         <v>315</v>
       </c>
@@ -4070,10 +4089,10 @@
       <c r="D73" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="E73" s="36" t="s">
+      <c r="E73" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="F73" s="36"/>
+      <c r="F73" s="38"/>
       <c r="G73" s="7" t="s">
         <v>309</v>
       </c>
@@ -4105,24 +4124,26 @@
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
-      <c r="K74" s="37"/>
-      <c r="L74" s="37"/>
+      <c r="K74" s="39"/>
+      <c r="L74" s="39"/>
       <c r="M74" s="2"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A75" s="33"/>
-      <c r="B75" s="33"/>
-      <c r="C75" s="33"/>
-      <c r="D75" s="33"/>
-      <c r="E75" s="33"/>
-      <c r="F75" s="33"/>
-      <c r="G75" s="33"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="33"/>
-      <c r="J75" s="33"/>
-      <c r="K75" s="34"/>
-      <c r="L75" s="34"/>
-      <c r="M75" s="35"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="36" t="s">
+        <v>321</v>
+      </c>
+      <c r="J75" s="36"/>
+      <c r="K75" s="36"/>
+      <c r="L75" s="36"/>
+      <c r="M75" s="34"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A76" s="4"/>
@@ -4133,20 +4154,28 @@
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
+      <c r="I76" s="60" t="s">
+        <v>322</v>
+      </c>
+      <c r="J76" s="60"/>
+      <c r="K76" s="60"/>
+      <c r="L76" s="60"/>
+      <c r="M76" s="34"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
+      <c r="A77" s="33"/>
+      <c r="B77" s="33"/>
+      <c r="C77" s="33"/>
+      <c r="D77" s="33"/>
+      <c r="E77" s="33"/>
+      <c r="F77" s="33"/>
+      <c r="G77" s="33"/>
+      <c r="H77" s="33"/>
+      <c r="I77" s="37"/>
+      <c r="J77" s="37"/>
+      <c r="K77" s="37"/>
+      <c r="L77" s="37"/>
+      <c r="M77" s="35"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A78" s="4"/>
@@ -4197,7 +4226,7 @@
       <c r="J81" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="87">
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:I2"/>
@@ -4274,6 +4303,8 @@
     <mergeCell ref="A63:L63"/>
     <mergeCell ref="E64:F64"/>
     <mergeCell ref="E65:F65"/>
+    <mergeCell ref="I75:L75"/>
+    <mergeCell ref="I77:L77"/>
     <mergeCell ref="E73:F73"/>
     <mergeCell ref="K74:L74"/>
     <mergeCell ref="E67:F67"/>
@@ -4282,6 +4313,7 @@
     <mergeCell ref="E70:F70"/>
     <mergeCell ref="E71:F71"/>
     <mergeCell ref="E72:F72"/>
+    <mergeCell ref="I76:L76"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G27" r:id="rId1" display="sanjay@gmail&quot;" xr:uid="{20C29829-2576-487E-9721-0A3014FAB7B9}"/>

--- a/Task-1-TestCase-by(sanjay srinivas T).xlsx
+++ b/Task-1-TestCase-by(sanjay srinivas T).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3fc2e1139c06ea87/Desktop/Tichi-assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{E7ABD9D2-253E-47D2-A19D-59E8DFE55EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E0C8BB7-4AEC-48E4-9CD5-2BCEA5989602}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{E7ABD9D2-253E-47D2-A19D-59E8DFE55EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1E44EFA-1CD0-4C77-A1D2-A7A37E5259DA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{1010C715-7696-41A7-9CF7-2C5ABBBA349D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="340">
   <si>
     <t>TEST CASE REPORT</t>
   </si>
@@ -48,9 +48,6 @@
     <t>TEST DESIGNED BY:</t>
   </si>
   <si>
-    <t>SANJAY SRINIVAS</t>
-  </si>
-  <si>
     <t>APPLICATION URL:</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
     <t>ENVIRONMENT:</t>
   </si>
   <si>
-    <t>WINDOWS 10/CHROME 138</t>
-  </si>
-  <si>
     <t>TESTING STARTED DATE:</t>
   </si>
   <si>
@@ -345,15 +339,9 @@
     <t>high</t>
   </si>
   <si>
-    <t>correct the login email format</t>
-  </si>
-  <si>
     <t>TC_ID_13</t>
   </si>
   <si>
-    <t>Verify the application rejects an email address without a domain name</t>
-  </si>
-  <si>
     <t>enter email without domain name</t>
   </si>
   <si>
@@ -999,17 +987,80 @@
     <t>sign in page is redirected to home page of website successfully</t>
   </si>
   <si>
-    <t>TESTED BY: SANJAY SRINIVAS T</t>
-  </si>
-  <si>
     <t>PROJECT DETAILS ABOVE 9TH ROW</t>
+  </si>
+  <si>
+    <t>TC_ID_54</t>
+  </si>
+  <si>
+    <t>TC_ID_55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verify login using email after google sign in account </t>
+  </si>
+  <si>
+    <t>Verify the application rejects an email address without a  domain extension</t>
+  </si>
+  <si>
+    <t>user has aready created account using continue with google and logged out</t>
+  </si>
+  <si>
+    <t>open application,click signin,enter the same gmail id which is previously used in continue with google</t>
+  </si>
+  <si>
+    <t>enter google id which is used in continue with google</t>
+  </si>
+  <si>
+    <t>password page is displayed even the password was not created during sign in</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>application should recognize the account was created using continue with google authentication so (1)redirect to the  google sign in page (2)display message "continue with google or set password using forgot password"</t>
+  </si>
+  <si>
+    <t>Forgot password</t>
+  </si>
+  <si>
+    <t>verify password for google sign in account</t>
+  </si>
+  <si>
+    <t>user account exist and already created using google sign in</t>
+  </si>
+  <si>
+    <t>(1)open login page.(2)enter the registered google email  id.(3)click continue.(4)click forgot pssword.(5)click send verification .(6)check for the mail from the website in you gmail.(7)click reset password in mail.(8)reset with newly created password as same as in both password field and confirm field.(9)then finaly click reset password.</t>
+  </si>
+  <si>
+    <t>existing google account email which used in continue with google</t>
+  </si>
+  <si>
+    <t>password reset email should be sent successfully.user should be able to create a password and log in successfully using the email and password for all other times</t>
+  </si>
+  <si>
+    <t>password reset email is received to the mail and user able to create the password and login successfully.</t>
+  </si>
+  <si>
+    <t>SANJAY SRINIVAS T</t>
+  </si>
+  <si>
+    <t>REPORTED BY: SANJAY SRINIVAS T</t>
+  </si>
+  <si>
+    <t>correct the acceptancy of login email format</t>
+  </si>
+  <si>
+    <t>WINDOWS 10/CHROME 138/MicroSoft Edge</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1053,14 +1104,6 @@
       <family val="1"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
@@ -1068,6 +1111,19 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -1324,7 +1380,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1336,7 +1392,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1387,7 +1443,7 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="9" xfId="10" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1417,49 +1473,44 @@
     <xf numFmtId="0" fontId="5" fillId="14" borderId="11" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="9" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="15" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="12" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1471,25 +1522,36 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="12" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="15" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="9" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="14" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="14" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="20% - Accent1" xfId="3" builtinId="30"/>
@@ -1511,6 +1573,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFE32D2D"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1819,13 +1886,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D32FFA9E-8333-43FD-9656-16E917A04A3E}">
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
     <col min="2" max="2" width="21.54296875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.81640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.90625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.54296875" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.1796875" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.7265625" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.36328125" style="1" customWidth="1"/>
@@ -1833,372 +1900,372 @@
     <col min="9" max="9" width="22.36328125" style="1" customWidth="1"/>
     <col min="10" max="10" width="13.81640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="10.7265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.54296875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.54296875" style="1" customWidth="1"/>
     <col min="13" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="54"/>
+      <c r="B2" s="37"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="55" t="s">
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" ht="20.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A3" s="54" t="s">
+      <c r="B3" s="37"/>
+      <c r="C3" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="59" t="s">
+      <c r="D3" s="62"/>
+      <c r="E3" s="3"/>
+      <c r="G3" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="59"/>
-      <c r="E3" s="3"/>
-      <c r="G3" s="54" t="s">
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="38" t="s">
+        <v>336</v>
+      </c>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A4" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A4" s="54" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="38" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="G4" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="54"/>
-      <c r="C4" s="55" t="s">
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="39">
+        <v>46029</v>
+      </c>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A5" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="G4" s="54" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="56">
-        <v>46029</v>
-      </c>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A5" s="57" t="s">
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="G5" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="G5" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="56">
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="39">
         <v>46060</v>
       </c>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A6" s="39"/>
-      <c r="B6" s="39"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="E9" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="F9" s="47"/>
+      <c r="G9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="49" t="s">
+      <c r="H9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="5" t="s">
+      <c r="I9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="J9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-      <c r="G10" s="52"/>
-      <c r="H10" s="52"/>
-      <c r="I10" s="52"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="52"/>
-      <c r="L10" s="53"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="50"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="D11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="E11" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="40" t="s">
+      <c r="F11" s="42"/>
+      <c r="G11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="41"/>
-      <c r="G11" s="7" t="s">
+      <c r="I11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="H11" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>32</v>
-      </c>
       <c r="J11" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M11" s="2"/>
     </row>
     <row r="12" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="9" t="s">
+      <c r="E12" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="F12" s="42"/>
+      <c r="G12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="40" t="s">
+      <c r="I12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="41"/>
-      <c r="G12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>39</v>
-      </c>
       <c r="J12" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A13" s="42"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="44"/>
+      <c r="A13" s="51"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="53"/>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="E14" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="F14" s="42"/>
+      <c r="G14" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="40" t="s">
+      <c r="I14" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="41"/>
-      <c r="G14" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>46</v>
-      </c>
       <c r="J14" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M14" s="2"/>
     </row>
     <row r="15" spans="1:13" ht="90" x14ac:dyDescent="0.4">
       <c r="A15" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="G15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="I15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F15" s="41"/>
-      <c r="G15" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="11" t="s">
+      <c r="J15" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K15" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>51</v>
-      </c>
       <c r="L15" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M15" s="2"/>
     </row>
     <row r="16" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="F16" s="42"/>
+      <c r="G16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="I16" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>55</v>
-      </c>
       <c r="J16" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M16" s="2"/>
     </row>
@@ -2219,112 +2286,112 @@
     </row>
     <row r="18" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A18" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="D18" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="F18" s="42"/>
+      <c r="G18" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="40" t="s">
+      <c r="I18" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="41"/>
-      <c r="G18" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>61</v>
-      </c>
       <c r="J18" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M18" s="2"/>
     </row>
     <row r="19" spans="1:13" ht="72" x14ac:dyDescent="0.4">
       <c r="A19" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="9" t="s">
+      <c r="E19" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="F19" s="42"/>
+      <c r="G19" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="40" t="s">
+      <c r="H19" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="41"/>
-      <c r="G19" s="7" t="s">
+      <c r="I19" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H19" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>68</v>
-      </c>
       <c r="J19" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13" ht="72" x14ac:dyDescent="0.4">
       <c r="A20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="17" t="s">
+      <c r="E20" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="F20" s="42"/>
+      <c r="G20" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="40" t="s">
+      <c r="H20" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="F20" s="41"/>
-      <c r="G20" s="7" t="s">
+      <c r="I20" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>75</v>
-      </c>
       <c r="J20" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M20" s="2"/>
     </row>
@@ -2345,1805 +2412,1847 @@
     </row>
     <row r="22" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="D22" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="E22" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="F22" s="42"/>
+      <c r="G22" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="40" t="s">
+      <c r="I22" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="F22" s="41"/>
-      <c r="G22" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>82</v>
-      </c>
       <c r="J22" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L22" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M22" s="2"/>
     </row>
     <row r="23" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A23" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C23" s="9" t="s">
+      <c r="F23" s="42"/>
+      <c r="G23" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="40" t="s">
+      <c r="H23" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="41"/>
-      <c r="G23" s="7" t="s">
+      <c r="I23" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H23" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>88</v>
-      </c>
       <c r="J23" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M23" s="2"/>
     </row>
     <row r="24" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A24" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="9" t="s">
+      <c r="F24" s="42"/>
+      <c r="G24" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="40" t="s">
+      <c r="H24" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="41"/>
-      <c r="G24" s="7" t="s">
+      <c r="I24" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="H24" s="11" t="s">
+      <c r="J24" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="25" spans="1:13" ht="116" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="B25" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="J24" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M24" s="2"/>
-    </row>
-    <row r="25" spans="1:13" ht="72" x14ac:dyDescent="0.4">
-      <c r="A25" s="7" t="s">
+      <c r="D25" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="9" t="s">
+      <c r="F25" s="42"/>
+      <c r="G25" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" s="40" t="s">
+      <c r="H25" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="41"/>
-      <c r="G25" s="7" t="s">
+      <c r="I25" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="H25" s="11" t="s">
+      <c r="J25" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="K25" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="J25" s="22" t="s">
+      <c r="L25" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="1:13" ht="107" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="K25" s="22" t="s">
+      <c r="B26" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="L25" s="22" t="s">
+      <c r="F26" s="42"/>
+      <c r="G26" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="M25" s="2"/>
-    </row>
-    <row r="26" spans="1:13" ht="72" x14ac:dyDescent="0.4">
-      <c r="A26" s="7" t="s">
+      <c r="H26" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="9" t="s">
+      <c r="I26" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D26" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="46" t="s">
+      <c r="J26" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" spans="1:13" ht="218" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F26" s="41"/>
-      <c r="G26" s="23" t="s">
+      <c r="B27" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="E27" s="55" t="s">
+        <v>323</v>
+      </c>
+      <c r="F27" s="60"/>
+      <c r="G27" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="J27" s="61" t="s">
+        <v>326</v>
+      </c>
+      <c r="K27" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="L27" s="61" t="s">
+        <v>327</v>
+      </c>
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" spans="1:13" ht="282" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="E28" s="55" t="s">
+        <v>332</v>
+      </c>
+      <c r="F28" s="60"/>
+      <c r="G28" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" spans="1:13" ht="90" x14ac:dyDescent="0.4">
+      <c r="A29" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="D29" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="56" t="s">
         <v>108</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="F29" s="56"/>
+      <c r="G29" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M26" s="2"/>
-    </row>
-    <row r="27" spans="1:13" ht="90" x14ac:dyDescent="0.4">
-      <c r="A27" s="7" t="s">
+      <c r="H29" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="9" t="s">
+      <c r="I29" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="F27" s="38"/>
-      <c r="G27" s="7" t="s">
+      <c r="J29" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+      <c r="A30" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="H27" s="11" t="s">
+      <c r="D30" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="I27" s="12" t="s">
+      <c r="E30" s="56" t="s">
         <v>115</v>
       </c>
-      <c r="J27" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M27" s="2"/>
-    </row>
-    <row r="28" spans="1:13" ht="36" x14ac:dyDescent="0.4">
-      <c r="A28" s="7" t="s">
+      <c r="F30" s="56"/>
+      <c r="G30" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="17" t="s">
+      <c r="I30" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="D28" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="38" t="s">
+      <c r="J30" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+      <c r="A31" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F28" s="38"/>
-      <c r="G28" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H28" s="11" t="s">
+      <c r="D31" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="E31" s="56" t="s">
         <v>121</v>
       </c>
-      <c r="J28" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M28" s="2"/>
-    </row>
-    <row r="29" spans="1:13" ht="36" x14ac:dyDescent="0.4">
-      <c r="A29" s="7" t="s">
+      <c r="F31" s="56"/>
+      <c r="G31" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="9" t="s">
+      <c r="H31" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="I31" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="E29" s="38" t="s">
-        <v>125</v>
-      </c>
-      <c r="F29" s="38"/>
-      <c r="G29" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="I29" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M29" s="2"/>
-    </row>
-    <row r="30" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A30" s="25" t="s">
-        <v>129</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="D30" s="28" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="F30" s="45"/>
-      <c r="G30" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="H30" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="I30" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="J30" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="K30" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="L30" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="M30" s="2"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A31" s="42"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="44"/>
+      <c r="J31" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L31" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A32" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="54"/>
+      <c r="G32" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="I32" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="J32" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="K32" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A33" s="51"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="53"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A34" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="56"/>
+      <c r="G34" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H34" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="I34" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E32" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F32" s="38"/>
-      <c r="G32" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="I32" s="12" t="s">
-        <v>140</v>
-      </c>
-      <c r="J32" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K32" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L32" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M32" s="2"/>
-    </row>
-    <row r="33" spans="1:13" ht="36" x14ac:dyDescent="0.4">
-      <c r="A33" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E33" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="38"/>
-      <c r="G33" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="I33" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L33" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M33" s="2"/>
-    </row>
-    <row r="34" spans="1:13" ht="36" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E34" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F34" s="38"/>
-      <c r="G34" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>150</v>
-      </c>
       <c r="J34" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L34" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M34" s="2"/>
     </row>
     <row r="35" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A35" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="56"/>
+      <c r="G35" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="J35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L35" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+      <c r="A36" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="B35" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E35" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F35" s="38"/>
-      <c r="G35" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="I35" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="J35" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K35" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L35" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M35" s="2"/>
-    </row>
-    <row r="36" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A36" s="7" t="s">
-        <v>155</v>
-      </c>
       <c r="B36" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D36" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E36" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F36" s="38"/>
+        <v>143</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="56"/>
       <c r="G36" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="I36" s="12" t="s">
-        <v>158</v>
+        <v>145</v>
+      </c>
+      <c r="I36" s="24" t="s">
+        <v>146</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L36" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M36" s="2"/>
     </row>
     <row r="37" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A37" s="7" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E37" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="F37" s="38"/>
+        <v>144</v>
+      </c>
+      <c r="E37" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="56"/>
       <c r="G37" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="I37" s="12" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L37" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M37" s="2"/>
     </row>
     <row r="38" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A38" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E38" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F38" s="56"/>
+      <c r="G38" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L38" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+      <c r="A39" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E38" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="F38" s="38"/>
-      <c r="G38" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="J38" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K38" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L38" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A39" s="7" t="s">
-        <v>167</v>
-      </c>
       <c r="B39" s="8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E39" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="F39" s="38"/>
+        <v>113</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E39" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="F39" s="56"/>
       <c r="G39" s="7" t="s">
-        <v>126</v>
+        <v>28</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L39" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M39" s="2"/>
     </row>
     <row r="40" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A40" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" s="56" t="s">
+        <v>156</v>
+      </c>
+      <c r="F40" s="56"/>
+      <c r="G40" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="J40" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L40" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M40" s="2"/>
+    </row>
+    <row r="41" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A41" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="9" t="s">
+      <c r="B41" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E41" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="F41" s="56"/>
+      <c r="G41" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="J41" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K41" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M41" s="2"/>
+    </row>
+    <row r="42" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A42" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E42" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="56"/>
+      <c r="G42" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H42" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I42" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L42" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M42" s="2"/>
+    </row>
+    <row r="43" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+      <c r="A43" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="D40" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F40" s="38"/>
-      <c r="G40" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H40" s="11" t="s">
+      <c r="D43" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="56"/>
+      <c r="G43" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="I40" s="24" t="s">
+      <c r="I43" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="J40" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K40" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L40" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M40" s="2"/>
-    </row>
-    <row r="41" spans="1:13" ht="36" x14ac:dyDescent="0.4">
-      <c r="A41" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="C41" s="9" t="s">
+      <c r="J43" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A44" s="51"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="52"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
+      <c r="M44" s="2"/>
+    </row>
+    <row r="45" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A45" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B45" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D41" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E41" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="38"/>
-      <c r="G41" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H41" s="11" t="s">
+      <c r="C45" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="D45" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45" s="56" t="s">
         <v>179</v>
       </c>
-      <c r="J41" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K41" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L41" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M41" s="2"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A42" s="42"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="44"/>
-      <c r="M42" s="2"/>
-    </row>
-    <row r="43" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A43" s="7" t="s">
+      <c r="F45" s="56"/>
+      <c r="G45" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="H45" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="I45" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="D43" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E43" s="38" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" s="38"/>
-      <c r="G43" s="7" t="s">
+      <c r="J45" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L45" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M45" s="2"/>
+    </row>
+    <row r="46" spans="1:13" ht="147" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C46" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="D46" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E46" s="56" t="s">
         <v>185</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="F46" s="56"/>
+      <c r="G46" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="J43" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K43" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L43" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M43" s="2"/>
-    </row>
-    <row r="44" spans="1:13" ht="126" x14ac:dyDescent="0.4">
-      <c r="A44" s="7" t="s">
+      <c r="H46" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C44" s="9" t="s">
+      <c r="I46" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="D44" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E44" s="38" t="s">
+      <c r="J46" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L46" s="32" t="s">
         <v>189</v>
       </c>
-      <c r="F44" s="38"/>
-      <c r="G44" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="H44" s="11" t="s">
+      <c r="M46" s="2"/>
+    </row>
+    <row r="47" spans="1:13" ht="159" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C47" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="D47" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E47" s="56" t="s">
         <v>192</v>
       </c>
-      <c r="J44" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K44" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="L44" s="32" t="s">
+      <c r="F47" s="56"/>
+      <c r="G47" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="M44" s="2"/>
-    </row>
-    <row r="45" spans="1:13" ht="126" x14ac:dyDescent="0.4">
-      <c r="A45" s="7" t="s">
+      <c r="H47" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C45" s="9" t="s">
+      <c r="I47" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="D45" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="F45" s="38"/>
-      <c r="G45" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="I45" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K45" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="L45" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="M45" s="2"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A46" s="42"/>
-      <c r="B46" s="43"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="J46" s="43"/>
-      <c r="K46" s="43"/>
-      <c r="L46" s="44"/>
-      <c r="M46" s="2"/>
-    </row>
-    <row r="47" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A47" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E47" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="F47" s="38"/>
-      <c r="G47" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="I47" s="12" t="s">
-        <v>186</v>
-      </c>
       <c r="J47" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K47" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L47" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="K47" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L47" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A48" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>207</v>
-      </c>
-      <c r="F48" s="38"/>
-      <c r="G48" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="I48" s="24" t="s">
-        <v>192</v>
-      </c>
-      <c r="J48" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K48" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L48" s="13" t="s">
-        <v>30</v>
-      </c>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A48" s="51"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
+      <c r="K48" s="52"/>
+      <c r="L48" s="53"/>
       <c r="M48" s="2"/>
     </row>
     <row r="49" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A49" s="7" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E49" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="F49" s="38"/>
+        <v>144</v>
+      </c>
+      <c r="E49" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="F49" s="56"/>
       <c r="G49" s="7" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L49" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A50" s="42"/>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
-      <c r="K50" s="43"/>
-      <c r="L50" s="44"/>
+    <row r="50" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A50" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E50" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="F50" s="56"/>
+      <c r="G50" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="I50" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K50" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L50" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="M50" s="2"/>
     </row>
     <row r="51" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A51" s="7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E51" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="F51" s="41"/>
+        <v>144</v>
+      </c>
+      <c r="E51" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="F51" s="56"/>
       <c r="G51" s="7" t="s">
-        <v>30</v>
+        <v>207</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="I51" s="12" t="s">
-        <v>218</v>
+        <v>195</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K51" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L51" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A52" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E52" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="F52" s="41"/>
-      <c r="G52" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H52" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="I52" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="J52" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K52" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L52" s="13" t="s">
-        <v>30</v>
-      </c>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A52" s="51"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
+      <c r="K52" s="52"/>
+      <c r="L52" s="53"/>
       <c r="M52" s="2"/>
     </row>
     <row r="53" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A53" s="7" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B53" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E53" s="41" t="s">
+        <v>212</v>
+      </c>
+      <c r="F53" s="42"/>
+      <c r="G53" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H53" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C53" s="9" t="s">
+      <c r="I53" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K53" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L53" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A54" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="D53" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E53" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="F53" s="41"/>
-      <c r="G53" s="7">
-        <v>9988776655</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="I53" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K53" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L53" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M53" s="2"/>
-    </row>
-    <row r="54" spans="1:13" ht="72" x14ac:dyDescent="0.4">
-      <c r="A54" s="7" t="s">
-        <v>229</v>
-      </c>
       <c r="B54" s="8" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E54" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="F54" s="41"/>
-      <c r="G54" s="7">
-        <v>998877665</v>
+        <v>211</v>
+      </c>
+      <c r="E54" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="F54" s="42"/>
+      <c r="G54" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L54" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M54" s="2"/>
     </row>
     <row r="55" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A55" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="F55" s="42"/>
+      <c r="G55" s="7">
+        <v>9988776655</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="J55" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K55" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L55" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M55" s="2"/>
+    </row>
+    <row r="56" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+      <c r="A56" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="B55" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C55" s="9" t="s">
+      <c r="B56" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E56" s="41" t="s">
+        <v>227</v>
+      </c>
+      <c r="F56" s="42"/>
+      <c r="G56" s="7">
+        <v>998877665</v>
+      </c>
+      <c r="H56" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="J56" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K56" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L56" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M56" s="2"/>
+    </row>
+    <row r="57" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A57" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E57" s="41" t="s">
+        <v>232</v>
+      </c>
+      <c r="F57" s="42"/>
+      <c r="G57" s="7">
+        <v>99887766554</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K57" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L57" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A58" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C58" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="D55" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E55" s="40" t="s">
+      <c r="D58" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E58" s="41" t="s">
         <v>236</v>
       </c>
-      <c r="F55" s="41"/>
-      <c r="G55" s="7">
-        <v>99887766554</v>
-      </c>
-      <c r="H55" s="11" t="s">
+      <c r="F58" s="42"/>
+      <c r="G58" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="I55" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="J55" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K55" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L55" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M55" s="2"/>
-    </row>
-    <row r="56" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A56" s="7" t="s">
+      <c r="H58" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="B56" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C56" s="9" t="s">
+      <c r="I58" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="D56" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E56" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="F56" s="41"/>
-      <c r="G56" s="7" t="s">
+      <c r="J58" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K58" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L58" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A59" s="51"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="52"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="53"/>
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.4">
+      <c r="A60" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B60" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="C60" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="I56" s="12" t="s">
+      <c r="D60" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E60" s="41" t="s">
         <v>243</v>
       </c>
-      <c r="J56" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K56" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L56" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M56" s="2"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A57" s="42"/>
-      <c r="B57" s="43"/>
-      <c r="C57" s="43"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="43"/>
-      <c r="H57" s="43"/>
-      <c r="I57" s="43"/>
-      <c r="J57" s="43"/>
-      <c r="K57" s="43"/>
-      <c r="L57" s="44"/>
-      <c r="M57" s="2"/>
-    </row>
-    <row r="58" spans="1:13" ht="90" x14ac:dyDescent="0.4">
-      <c r="A58" s="7" t="s">
+      <c r="F60" s="42"/>
+      <c r="G60" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H60" s="11" t="s">
         <v>244</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="I60" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="C58" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E58" s="40" t="s">
-        <v>247</v>
-      </c>
-      <c r="F58" s="41"/>
-      <c r="G58" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="J58" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K58" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L58" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M58" s="2"/>
-    </row>
-    <row r="59" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A59" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E59" s="40" t="s">
-        <v>252</v>
-      </c>
-      <c r="F59" s="41"/>
-      <c r="G59" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="I59" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="J59" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K59" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L59" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M59" s="2"/>
-    </row>
-    <row r="60" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A60" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E60" s="40" t="s">
-        <v>258</v>
-      </c>
-      <c r="F60" s="41"/>
-      <c r="G60" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="H60" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="I60" s="12" t="s">
-        <v>260</v>
-      </c>
       <c r="J60" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L60" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M60" s="2"/>
     </row>
     <row r="61" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A61" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E61" s="41" t="s">
+        <v>248</v>
+      </c>
+      <c r="F61" s="42"/>
+      <c r="G61" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="J61" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K61" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L61" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M61" s="2"/>
+    </row>
+    <row r="62" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A62" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E62" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="F62" s="42"/>
+      <c r="G62" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="J62" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K62" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L62" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M62" s="2"/>
+    </row>
+    <row r="63" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A63" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E63" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="F63" s="42"/>
+      <c r="G63" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="H63" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="I63" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="J63" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K63" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L63" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M63" s="2"/>
+    </row>
+    <row r="64" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+      <c r="A64" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E64" s="41" t="s">
+        <v>265</v>
+      </c>
+      <c r="F64" s="42"/>
+      <c r="G64" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="H64" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="J64" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L64" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M64" s="2"/>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A65" s="51"/>
+      <c r="B65" s="52"/>
+      <c r="C65" s="52"/>
+      <c r="D65" s="52"/>
+      <c r="E65" s="52"/>
+      <c r="F65" s="52"/>
+      <c r="G65" s="52"/>
+      <c r="H65" s="52"/>
+      <c r="I65" s="52"/>
+      <c r="J65" s="52"/>
+      <c r="K65" s="52"/>
+      <c r="L65" s="53"/>
+      <c r="M65" s="2"/>
+    </row>
+    <row r="66" spans="1:13" ht="90" x14ac:dyDescent="0.4">
+      <c r="A66" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E66" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="F66" s="42"/>
+      <c r="G66" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="I66" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="C61" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E61" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="F61" s="41"/>
-      <c r="G61" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="H61" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="I61" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="J61" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K61" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L61" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M61" s="2"/>
-    </row>
-    <row r="62" spans="1:13" ht="72" x14ac:dyDescent="0.4">
-      <c r="A62" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E62" s="40" t="s">
-        <v>269</v>
-      </c>
-      <c r="F62" s="41"/>
-      <c r="G62" s="7" t="s">
+      <c r="J66" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K66" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L66" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M66" s="2"/>
+    </row>
+    <row r="67" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A67" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B67" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="H62" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="J62" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K62" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L62" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M62" s="2"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A63" s="42"/>
-      <c r="B63" s="43"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="43"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="43"/>
-      <c r="H63" s="43"/>
-      <c r="I63" s="43"/>
-      <c r="J63" s="43"/>
-      <c r="K63" s="43"/>
-      <c r="L63" s="44"/>
-      <c r="M63" s="2"/>
-    </row>
-    <row r="64" spans="1:13" ht="90" x14ac:dyDescent="0.4">
-      <c r="A64" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C64" s="9" t="s">
+      <c r="C67" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="D64" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E64" s="40" t="s">
+      <c r="D67" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E67" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="F64" s="41"/>
-      <c r="G64" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="H64" s="11" t="s">
+      <c r="F67" s="42"/>
+      <c r="G67" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="I64" s="12" t="s">
-        <v>249</v>
-      </c>
-      <c r="J64" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K64" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L64" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M64" s="2"/>
-    </row>
-    <row r="65" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A65" s="7" t="s">
+      <c r="H67" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E65" s="40" t="s">
-        <v>280</v>
-      </c>
-      <c r="F65" s="41"/>
-      <c r="G65" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H65" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="I65" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="J65" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K65" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L65" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M65" s="2"/>
-    </row>
-    <row r="66" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A66" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E66" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="F66" s="41"/>
-      <c r="G66" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H66" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="J66" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K66" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L66" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M66" s="2"/>
-    </row>
-    <row r="67" spans="1:13" ht="36" x14ac:dyDescent="0.4">
-      <c r="A67" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E67" s="40" t="s">
-        <v>290</v>
-      </c>
-      <c r="F67" s="41"/>
-      <c r="G67" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H67" s="11" t="s">
-        <v>291</v>
-      </c>
       <c r="I67" s="12" t="s">
-        <v>292</v>
+        <v>251</v>
       </c>
       <c r="J67" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K67" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L67" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M67" s="2"/>
     </row>
     <row r="68" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A68" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E68" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="F68" s="42"/>
+      <c r="G68" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="J68" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K68" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L68" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M68" s="2"/>
+    </row>
+    <row r="69" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+      <c r="A69" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E69" s="41" t="s">
+        <v>286</v>
+      </c>
+      <c r="F69" s="42"/>
+      <c r="G69" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="J69" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K69" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L69" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M69" s="2"/>
+    </row>
+    <row r="70" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A70" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E70" s="41" t="s">
+        <v>291</v>
+      </c>
+      <c r="F70" s="42"/>
+      <c r="G70" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="H70" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="B68" s="8" t="s">
-        <v>274</v>
-      </c>
-      <c r="C68" s="9" t="s">
+      <c r="I70" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="D68" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E68" s="40" t="s">
-        <v>295</v>
-      </c>
-      <c r="F68" s="41"/>
-      <c r="G68" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="H68" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>298</v>
-      </c>
-      <c r="J68" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K68" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L68" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M68" s="2"/>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A69" s="42"/>
-      <c r="B69" s="43"/>
-      <c r="C69" s="43"/>
-      <c r="D69" s="43"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="43"/>
-      <c r="H69" s="43"/>
-      <c r="I69" s="43"/>
-      <c r="J69" s="43"/>
-      <c r="K69" s="43"/>
-      <c r="L69" s="44"/>
-      <c r="M69" s="2"/>
-    </row>
-    <row r="70" spans="1:13" ht="72" x14ac:dyDescent="0.4">
-      <c r="A70" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E70" s="40" t="s">
-        <v>302</v>
-      </c>
-      <c r="F70" s="41"/>
-      <c r="G70" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="H70" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="I70" s="12" t="s">
-        <v>305</v>
-      </c>
       <c r="J70" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L70" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M70" s="2"/>
     </row>
-    <row r="71" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A71" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="C71" s="17" t="s">
-        <v>307</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E71" s="40" t="s">
-        <v>308</v>
-      </c>
-      <c r="F71" s="41"/>
-      <c r="G71" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="H71" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="I71" s="12" t="s">
-        <v>311</v>
-      </c>
-      <c r="J71" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K71" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L71" s="13" t="s">
-        <v>30</v>
-      </c>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A71" s="51"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
+      <c r="J71" s="52"/>
+      <c r="K71" s="52"/>
+      <c r="L71" s="53"/>
       <c r="M71" s="2"/>
     </row>
     <row r="72" spans="1:13" ht="72" x14ac:dyDescent="0.4">
       <c r="A72" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E72" s="41" t="s">
+        <v>298</v>
+      </c>
+      <c r="F72" s="42"/>
+      <c r="G72" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H72" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="I72" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="J72" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K72" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L72" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M72" s="2"/>
+    </row>
+    <row r="73" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A73" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E73" s="41" t="s">
+        <v>304</v>
+      </c>
+      <c r="F73" s="42"/>
+      <c r="G73" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="H73" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K73" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L73" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M73" s="2"/>
+    </row>
+    <row r="74" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+      <c r="A74" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E74" s="41" t="s">
+        <v>310</v>
+      </c>
+      <c r="F74" s="42"/>
+      <c r="G74" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H74" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="I74" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="B72" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="C72" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="D72" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E72" s="40" t="s">
+      <c r="J74" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K74" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L74" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M74" s="2"/>
+    </row>
+    <row r="75" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+      <c r="A75" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E75" s="56" t="s">
         <v>314</v>
       </c>
-      <c r="F72" s="41"/>
-      <c r="G72" s="7" t="s">
+      <c r="F75" s="56"/>
+      <c r="G75" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="H75" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="H72" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="I72" s="12" t="s">
+      <c r="I75" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="J72" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K72" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L72" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M72" s="2"/>
-    </row>
-    <row r="73" spans="1:13" ht="72" x14ac:dyDescent="0.4">
-      <c r="A73" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="E73" s="38" t="s">
-        <v>318</v>
-      </c>
-      <c r="F73" s="38"/>
-      <c r="G73" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="H73" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="I73" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="J73" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K73" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L73" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="M73" s="2"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="39"/>
-      <c r="L74" s="39"/>
-      <c r="M74" s="2"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="J75" s="36"/>
-      <c r="K75" s="36"/>
-      <c r="L75" s="36"/>
-      <c r="M75" s="34"/>
+      <c r="J75" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L75" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M75" s="2"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A76" s="4"/>
@@ -4154,28 +4263,28 @@
       <c r="F76" s="4"/>
       <c r="G76" s="4"/>
       <c r="H76" s="4"/>
-      <c r="I76" s="60" t="s">
-        <v>322</v>
-      </c>
-      <c r="J76" s="60"/>
-      <c r="K76" s="60"/>
-      <c r="L76" s="60"/>
-      <c r="M76" s="34"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="43"/>
+      <c r="L76" s="43"/>
+      <c r="M76" s="2"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A77" s="33"/>
-      <c r="B77" s="33"/>
-      <c r="C77" s="33"/>
-      <c r="D77" s="33"/>
-      <c r="E77" s="33"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="33"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="37"/>
-      <c r="J77" s="37"/>
-      <c r="K77" s="37"/>
-      <c r="L77" s="37"/>
-      <c r="M77" s="35"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="57" t="s">
+        <v>337</v>
+      </c>
+      <c r="J77" s="57"/>
+      <c r="K77" s="57"/>
+      <c r="L77" s="57"/>
+      <c r="M77" s="34"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A78" s="4"/>
@@ -4186,20 +4295,28 @@
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
+      <c r="I78" s="59" t="s">
+        <v>317</v>
+      </c>
+      <c r="J78" s="59"/>
+      <c r="K78" s="59"/>
+      <c r="L78" s="59"/>
+      <c r="M78" s="34"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="4"/>
-      <c r="J79" s="4"/>
+      <c r="A79" s="33"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="33"/>
+      <c r="D79" s="33"/>
+      <c r="E79" s="33"/>
+      <c r="F79" s="33"/>
+      <c r="G79" s="33"/>
+      <c r="H79" s="33"/>
+      <c r="I79" s="58"/>
+      <c r="J79" s="58"/>
+      <c r="K79" s="58"/>
+      <c r="L79" s="58"/>
+      <c r="M79" s="35"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A80" s="4"/>
@@ -4225,24 +4342,93 @@
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
     </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
+      <c r="C82" s="4"/>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="4"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
+      <c r="C83" s="4"/>
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="4"/>
+      <c r="H83" s="4"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="87">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
+  <mergeCells count="89">
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="I79:L79"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="A71:L71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="I78:L78"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="A59:L59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="A65:L65"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E28:F28"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E6:F6"/>
@@ -4255,72 +4441,30 @@
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A42:L42"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="A46:L46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="A50:L50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="A57:L57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="A63:L63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="I75:L75"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="K74:L74"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="A69:L69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="I76:L76"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
   </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G27" r:id="rId1" display="sanjay@gmail&quot;" xr:uid="{20C29829-2576-487E-9721-0A3014FAB7B9}"/>
-    <hyperlink ref="G29" r:id="rId2" xr:uid="{D21CDC16-49F6-4309-96A9-2E51498E21C8}"/>
-    <hyperlink ref="G30" r:id="rId3" xr:uid="{E8D07DF6-8D59-44A0-9572-73626C8E4D0B}"/>
-    <hyperlink ref="G39" r:id="rId4" xr:uid="{DC0EB2BA-84FD-4926-A351-EE2D56BE34B2}"/>
-    <hyperlink ref="G59" r:id="rId5" xr:uid="{657EF47E-91F6-44AC-8CC5-5DBD1BCD4B49}"/>
+    <hyperlink ref="G29" r:id="rId1" display="sanjay@gmail&quot;" xr:uid="{20C29829-2576-487E-9721-0A3014FAB7B9}"/>
+    <hyperlink ref="G31" r:id="rId2" xr:uid="{D21CDC16-49F6-4309-96A9-2E51498E21C8}"/>
+    <hyperlink ref="G32" r:id="rId3" xr:uid="{E8D07DF6-8D59-44A0-9572-73626C8E4D0B}"/>
+    <hyperlink ref="G41" r:id="rId4" xr:uid="{DC0EB2BA-84FD-4926-A351-EE2D56BE34B2}"/>
+    <hyperlink ref="G61" r:id="rId5" xr:uid="{657EF47E-91F6-44AC-8CC5-5DBD1BCD4B49}"/>
     <hyperlink ref="C3" r:id="rId6" xr:uid="{3EEF9359-C10C-4BC6-8CE6-AE96837A9394}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Task-1-TestCase-by(sanjay srinivas T).xlsx
+++ b/Task-1-TestCase-by(sanjay srinivas T).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3fc2e1139c06ea87/Desktop/Tichi-assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{E7ABD9D2-253E-47D2-A19D-59E8DFE55EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1E44EFA-1CD0-4C77-A1D2-A7A37E5259DA}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{E7ABD9D2-253E-47D2-A19D-59E8DFE55EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17E1099C-3FD6-4D01-8F55-1B1770A2066F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{1010C715-7696-41A7-9CF7-2C5ABBBA349D}"/>
   </bookViews>
@@ -1479,19 +1479,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="12" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="9" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="15" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1500,8 +1496,24 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1522,32 +1534,20 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="15" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="9" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="12" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="14" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1905,116 +1905,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
+      <c r="B2" s="57"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="38" t="s">
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58" t="s">
         <v>336</v>
       </c>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
       <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="20.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="37"/>
+      <c r="B3" s="57"/>
       <c r="C3" s="62" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="62"/>
       <c r="E3" s="3"/>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="38" t="s">
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58" t="s">
         <v>336</v>
       </c>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="38" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="38"/>
-      <c r="G4" s="37" t="s">
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="G4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="39">
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
+      <c r="J4" s="59">
         <v>46029</v>
       </c>
-      <c r="K4" s="38"/>
-      <c r="L4" s="38"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="38" t="s">
+      <c r="B5" s="60"/>
+      <c r="C5" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="G5" s="40" t="s">
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="G5" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="39">
+      <c r="H5" s="60"/>
+      <c r="I5" s="60"/>
+      <c r="J5" s="59">
         <v>46060</v>
       </c>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="40"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E7" s="44"/>
-      <c r="F7" s="44"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -2030,10 +2030,10 @@
       <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="46" t="s">
+      <c r="E9" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="47"/>
+      <c r="F9" s="53"/>
       <c r="G9" s="5" t="s">
         <v>17</v>
       </c>
@@ -2055,18 +2055,18 @@
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A10" s="48"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="49"/>
-      <c r="J10" s="49"/>
-      <c r="K10" s="49"/>
-      <c r="L10" s="50"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="55"/>
+      <c r="I10" s="55"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
+      <c r="L10" s="56"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13" ht="36" x14ac:dyDescent="0.4">
@@ -2144,18 +2144,18 @@
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A13" s="51"/>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="53"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="45"/>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A24" s="7" t="s">
         <v>87</v>
       </c>
@@ -2571,7 +2571,7 @@
       <c r="D26" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="55" t="s">
+      <c r="E26" s="48" t="s">
         <v>102</v>
       </c>
       <c r="F26" s="42"/>
@@ -2608,10 +2608,10 @@
       <c r="D27" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="E27" s="55" t="s">
+      <c r="E27" s="48" t="s">
         <v>323</v>
       </c>
-      <c r="F27" s="60"/>
+      <c r="F27" s="49"/>
       <c r="G27" s="23" t="s">
         <v>324</v>
       </c>
@@ -2621,13 +2621,13 @@
       <c r="I27" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="J27" s="61" t="s">
+      <c r="J27" s="36" t="s">
         <v>326</v>
       </c>
-      <c r="K27" s="61" t="s">
+      <c r="K27" s="36" t="s">
         <v>327</v>
       </c>
-      <c r="L27" s="61" t="s">
+      <c r="L27" s="36" t="s">
         <v>327</v>
       </c>
       <c r="M27" s="2"/>
@@ -2645,10 +2645,10 @@
       <c r="D28" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="E28" s="55" t="s">
+      <c r="E28" s="48" t="s">
         <v>332</v>
       </c>
-      <c r="F28" s="60"/>
+      <c r="F28" s="49"/>
       <c r="G28" s="23" t="s">
         <v>333</v>
       </c>
@@ -2682,10 +2682,10 @@
       <c r="D29" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="56" t="s">
+      <c r="E29" s="39" t="s">
         <v>108</v>
       </c>
-      <c r="F29" s="56"/>
+      <c r="F29" s="39"/>
       <c r="G29" s="7" t="s">
         <v>109</v>
       </c>
@@ -2719,10 +2719,10 @@
       <c r="D30" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="E30" s="56" t="s">
+      <c r="E30" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="F30" s="56"/>
+      <c r="F30" s="39"/>
       <c r="G30" s="7" t="s">
         <v>28</v>
       </c>
@@ -2756,10 +2756,10 @@
       <c r="D31" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="E31" s="56" t="s">
+      <c r="E31" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="F31" s="56"/>
+      <c r="F31" s="39"/>
       <c r="G31" s="7" t="s">
         <v>122</v>
       </c>
@@ -2793,10 +2793,10 @@
       <c r="D32" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="54" t="s">
+      <c r="E32" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="F32" s="54"/>
+      <c r="F32" s="47"/>
       <c r="G32" s="25" t="s">
         <v>128</v>
       </c>
@@ -2818,18 +2818,18 @@
       <c r="M32" s="2"/>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A33" s="51"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
-      <c r="L33" s="53"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="44"/>
+      <c r="L33" s="45"/>
       <c r="M33" s="2"/>
     </row>
     <row r="34" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -2845,10 +2845,10 @@
       <c r="D34" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E34" s="56" t="s">
+      <c r="E34" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="56"/>
+      <c r="F34" s="39"/>
       <c r="G34" s="7" t="s">
         <v>28</v>
       </c>
@@ -2882,10 +2882,10 @@
       <c r="D35" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="E35" s="56" t="s">
+      <c r="E35" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="56"/>
+      <c r="F35" s="39"/>
       <c r="G35" s="7" t="s">
         <v>28</v>
       </c>
@@ -2919,10 +2919,10 @@
       <c r="D36" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="56"/>
+      <c r="F36" s="39"/>
       <c r="G36" s="7" t="s">
         <v>28</v>
       </c>
@@ -2956,10 +2956,10 @@
       <c r="D37" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="56" t="s">
+      <c r="E37" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="56"/>
+      <c r="F37" s="39"/>
       <c r="G37" s="7" t="s">
         <v>28</v>
       </c>
@@ -2993,10 +2993,10 @@
       <c r="D38" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="56" t="s">
+      <c r="E38" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="56"/>
+      <c r="F38" s="39"/>
       <c r="G38" s="7" t="s">
         <v>28</v>
       </c>
@@ -3030,10 +3030,10 @@
       <c r="D39" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E39" s="56" t="s">
+      <c r="E39" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="F39" s="56"/>
+      <c r="F39" s="39"/>
       <c r="G39" s="7" t="s">
         <v>28</v>
       </c>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="M39" s="2"/>
     </row>
-    <row r="40" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A40" s="7" t="s">
         <v>168</v>
       </c>
@@ -3067,10 +3067,10 @@
       <c r="D40" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E40" s="56" t="s">
+      <c r="E40" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="F40" s="56"/>
+      <c r="F40" s="39"/>
       <c r="G40" s="7" t="s">
         <v>28</v>
       </c>
@@ -3104,10 +3104,10 @@
       <c r="D41" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="56" t="s">
+      <c r="E41" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="F41" s="56"/>
+      <c r="F41" s="39"/>
       <c r="G41" s="7" t="s">
         <v>122</v>
       </c>
@@ -3141,10 +3141,10 @@
       <c r="D42" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E42" s="56" t="s">
+      <c r="E42" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="56"/>
+      <c r="F42" s="39"/>
       <c r="G42" s="7" t="s">
         <v>28</v>
       </c>
@@ -3178,10 +3178,10 @@
       <c r="D43" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E43" s="56" t="s">
+      <c r="E43" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="F43" s="56"/>
+      <c r="F43" s="39"/>
       <c r="G43" s="7" t="s">
         <v>28</v>
       </c>
@@ -3203,18 +3203,18 @@
       <c r="M43" s="2"/>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A44" s="51"/>
-      <c r="B44" s="52"/>
-      <c r="C44" s="52"/>
-      <c r="D44" s="52"/>
-      <c r="E44" s="52"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="52"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="52"/>
-      <c r="J44" s="52"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
+      <c r="A44" s="43"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="44"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="44"/>
+      <c r="L44" s="45"/>
       <c r="M44" s="2"/>
     </row>
     <row r="45" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -3230,10 +3230,10 @@
       <c r="D45" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E45" s="56" t="s">
+      <c r="E45" s="39" t="s">
         <v>179</v>
       </c>
-      <c r="F45" s="56"/>
+      <c r="F45" s="39"/>
       <c r="G45" s="7" t="s">
         <v>180</v>
       </c>
@@ -3267,10 +3267,10 @@
       <c r="D46" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E46" s="56" t="s">
+      <c r="E46" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="F46" s="56"/>
+      <c r="F46" s="39"/>
       <c r="G46" s="7" t="s">
         <v>186</v>
       </c>
@@ -3304,10 +3304,10 @@
       <c r="D47" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="56" t="s">
+      <c r="E47" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="F47" s="56"/>
+      <c r="F47" s="39"/>
       <c r="G47" s="7" t="s">
         <v>193</v>
       </c>
@@ -3329,18 +3329,18 @@
       <c r="M47" s="2"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A48" s="51"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="52"/>
-      <c r="D48" s="52"/>
-      <c r="E48" s="52"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="52"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="52"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="52"/>
-      <c r="L48" s="53"/>
+      <c r="A48" s="43"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="45"/>
       <c r="M48" s="2"/>
     </row>
     <row r="49" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -3356,10 +3356,10 @@
       <c r="D49" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E49" s="56" t="s">
+      <c r="E49" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="F49" s="56"/>
+      <c r="F49" s="39"/>
       <c r="G49" s="7" t="s">
         <v>200</v>
       </c>
@@ -3393,10 +3393,10 @@
       <c r="D50" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E50" s="56" t="s">
+      <c r="E50" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="F50" s="56"/>
+      <c r="F50" s="39"/>
       <c r="G50" s="7" t="s">
         <v>204</v>
       </c>
@@ -3430,10 +3430,10 @@
       <c r="D51" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E51" s="56" t="s">
+      <c r="E51" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="F51" s="56"/>
+      <c r="F51" s="39"/>
       <c r="G51" s="7" t="s">
         <v>207</v>
       </c>
@@ -3455,18 +3455,18 @@
       <c r="M51" s="2"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A52" s="51"/>
-      <c r="B52" s="52"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="52"/>
-      <c r="J52" s="52"/>
-      <c r="K52" s="52"/>
-      <c r="L52" s="53"/>
+      <c r="A52" s="43"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
+      <c r="I52" s="44"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="44"/>
+      <c r="L52" s="45"/>
       <c r="M52" s="2"/>
     </row>
     <row r="53" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A54" s="7" t="s">
         <v>225</v>
       </c>
@@ -3692,21 +3692,21 @@
       <c r="M58" s="2"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A59" s="51"/>
-      <c r="B59" s="52"/>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="52"/>
-      <c r="I59" s="52"/>
-      <c r="J59" s="52"/>
-      <c r="K59" s="52"/>
-      <c r="L59" s="53"/>
+      <c r="A59" s="43"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="44"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="44"/>
+      <c r="I59" s="44"/>
+      <c r="J59" s="44"/>
+      <c r="K59" s="44"/>
+      <c r="L59" s="45"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" ht="72" x14ac:dyDescent="0.4">
       <c r="A60" s="7" t="s">
         <v>252</v>
       </c>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A61" s="7" t="s">
         <v>257</v>
       </c>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="M62" s="2"/>
     </row>
-    <row r="63" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A63" s="7" t="s">
         <v>269</v>
       </c>
@@ -3892,18 +3892,18 @@
       <c r="M64" s="2"/>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A65" s="51"/>
-      <c r="B65" s="52"/>
-      <c r="C65" s="52"/>
-      <c r="D65" s="52"/>
-      <c r="E65" s="52"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="52"/>
-      <c r="H65" s="52"/>
-      <c r="I65" s="52"/>
-      <c r="J65" s="52"/>
-      <c r="K65" s="52"/>
-      <c r="L65" s="53"/>
+      <c r="A65" s="43"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
+      <c r="I65" s="44"/>
+      <c r="J65" s="44"/>
+      <c r="K65" s="44"/>
+      <c r="L65" s="45"/>
       <c r="M65" s="2"/>
     </row>
     <row r="66" spans="1:13" ht="90" x14ac:dyDescent="0.4">
@@ -4092,18 +4092,18 @@
       <c r="M70" s="2"/>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A71" s="51"/>
-      <c r="B71" s="52"/>
-      <c r="C71" s="52"/>
-      <c r="D71" s="52"/>
-      <c r="E71" s="52"/>
-      <c r="F71" s="52"/>
-      <c r="G71" s="52"/>
-      <c r="H71" s="52"/>
-      <c r="I71" s="52"/>
-      <c r="J71" s="52"/>
-      <c r="K71" s="52"/>
-      <c r="L71" s="53"/>
+      <c r="A71" s="43"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="44"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="44"/>
+      <c r="F71" s="44"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="44"/>
+      <c r="I71" s="44"/>
+      <c r="J71" s="44"/>
+      <c r="K71" s="44"/>
+      <c r="L71" s="45"/>
       <c r="M71" s="2"/>
     </row>
     <row r="72" spans="1:13" ht="72" x14ac:dyDescent="0.4">
@@ -4230,10 +4230,10 @@
       <c r="D75" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E75" s="56" t="s">
+      <c r="E75" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="F75" s="56"/>
+      <c r="F75" s="39"/>
       <c r="G75" s="7" t="s">
         <v>305</v>
       </c>
@@ -4265,8 +4265,8 @@
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
-      <c r="K76" s="43"/>
-      <c r="L76" s="43"/>
+      <c r="K76" s="40"/>
+      <c r="L76" s="40"/>
       <c r="M76" s="2"/>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.4">
@@ -4278,12 +4278,12 @@
       <c r="F77" s="4"/>
       <c r="G77" s="4"/>
       <c r="H77" s="4"/>
-      <c r="I77" s="57" t="s">
+      <c r="I77" s="37" t="s">
         <v>337</v>
       </c>
-      <c r="J77" s="57"/>
-      <c r="K77" s="57"/>
-      <c r="L77" s="57"/>
+      <c r="J77" s="37"/>
+      <c r="K77" s="37"/>
+      <c r="L77" s="37"/>
       <c r="M77" s="34"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.4">
@@ -4295,12 +4295,12 @@
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
       <c r="H78" s="4"/>
-      <c r="I78" s="59" t="s">
+      <c r="I78" s="46" t="s">
         <v>317</v>
       </c>
-      <c r="J78" s="59"/>
-      <c r="K78" s="59"/>
-      <c r="L78" s="59"/>
+      <c r="J78" s="46"/>
+      <c r="K78" s="46"/>
+      <c r="L78" s="46"/>
       <c r="M78" s="34"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.4">
@@ -4312,10 +4312,10 @@
       <c r="F79" s="33"/>
       <c r="G79" s="33"/>
       <c r="H79" s="33"/>
-      <c r="I79" s="58"/>
-      <c r="J79" s="58"/>
-      <c r="K79" s="58"/>
-      <c r="L79" s="58"/>
+      <c r="I79" s="38"/>
+      <c r="J79" s="38"/>
+      <c r="K79" s="38"/>
+      <c r="L79" s="38"/>
       <c r="M79" s="35"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.4">
@@ -4368,53 +4368,34 @@
     </row>
   </sheetData>
   <mergeCells count="89">
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="I79:L79"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="A71:L71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="I78:L78"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="A59:L59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="A65:L65"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="A52:L52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E19:F19"/>
@@ -4429,34 +4410,53 @@
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="A52:L52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="A59:L59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="A65:L65"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="I77:L77"/>
+    <mergeCell ref="I79:L79"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="A71:L71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="I78:L78"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>

--- a/Task-1-TestCase-by(sanjay srinivas T).xlsx
+++ b/Task-1-TestCase-by(sanjay srinivas T).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3fc2e1139c06ea87/Desktop/Tichi-assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{E7ABD9D2-253E-47D2-A19D-59E8DFE55EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17E1099C-3FD6-4D01-8F55-1B1770A2066F}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{E7ABD9D2-253E-47D2-A19D-59E8DFE55EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6617B6-2B6F-4F11-8D28-05CD7AD526AB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{1010C715-7696-41A7-9CF7-2C5ABBBA349D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="358">
   <si>
     <t>TEST CASE REPORT</t>
   </si>
@@ -1054,6 +1054,60 @@
   </si>
   <si>
     <t>WINDOWS 10/CHROME 138/MicroSoft Edge</t>
+  </si>
+  <si>
+    <t>TC_ID_56</t>
+  </si>
+  <si>
+    <t>TC_ID_57</t>
+  </si>
+  <si>
+    <t>TC_ID_58</t>
+  </si>
+  <si>
+    <t>verify maximum length of validation for email addreass field</t>
+  </si>
+  <si>
+    <t>user is on login page</t>
+  </si>
+  <si>
+    <t>(1)open login page,(2)enter email address with more length of 254 character,(3)click continue</t>
+  </si>
+  <si>
+    <t>aaaaaa(254+chars)..@gmail.com</t>
+  </si>
+  <si>
+    <t>application should restrict the maximum input length and should display message like "email address should with in this length  (n)",and user should not allowed to enter next page</t>
+  </si>
+  <si>
+    <t>application accept the excessively long email input without any message</t>
+  </si>
+  <si>
+    <t>should display any message and restrict to enter</t>
+  </si>
+  <si>
+    <t>verify maximum length validation for first name</t>
+  </si>
+  <si>
+    <t>(1).enter to signup page,(2)enter more characters for the first name field (100 character)</t>
+  </si>
+  <si>
+    <t>aaaaaaaaa..100+</t>
+  </si>
+  <si>
+    <t>application should restrict the length of input name and should display message like "name should with in this character"</t>
+  </si>
+  <si>
+    <t>application accept the unlimited characters without displaying any message</t>
+  </si>
+  <si>
+    <t>should display message for mentioning the length</t>
+  </si>
+  <si>
+    <t>(1).enter to signup page,(2)enter more characters for the last name field (100 character)</t>
+  </si>
+  <si>
+    <t>bbbbbbbbb..(100+)</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1434,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1482,38 +1536,32 @@
     <xf numFmtId="0" fontId="6" fillId="15" borderId="9" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="15" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="14" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="12" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1534,23 +1582,32 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="12" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="9" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" xfId="14" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="6" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="8" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="11" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="9" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="15" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="9" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="16">
@@ -1886,7 +1943,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D32FFA9E-8333-43FD-9656-16E917A04A3E}">
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
@@ -1895,7 +1952,7 @@
     <col min="4" max="4" width="22.54296875" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.1796875" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.7265625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25" style="1" customWidth="1"/>
     <col min="8" max="8" width="24.26953125" style="1" customWidth="1"/>
     <col min="9" max="9" width="22.36328125" style="1" customWidth="1"/>
     <col min="10" max="10" width="13.81640625" style="1" customWidth="1"/>
@@ -1905,116 +1962,116 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E1" s="61" t="s">
+      <c r="E1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
+      <c r="B2" s="38"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="58" t="s">
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
       <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" ht="20.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="62" t="s">
+      <c r="B3" s="38"/>
+      <c r="C3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="62"/>
+      <c r="D3" s="40"/>
       <c r="E3" s="3"/>
-      <c r="G3" s="57" t="s">
+      <c r="G3" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58" t="s">
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="39" t="s">
         <v>336</v>
       </c>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="58" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="39" t="s">
         <v>339</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="G4" s="57" t="s">
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="G4" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-      <c r="J4" s="59">
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="41">
         <v>46029</v>
       </c>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A5" s="60" t="s">
+      <c r="A5" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="60"/>
-      <c r="C5" s="58" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="G5" s="60" t="s">
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="G5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="59">
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="41">
         <v>46060</v>
       </c>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A6" s="40"/>
-      <c r="B6" s="40"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="E8" s="51"/>
-      <c r="F8" s="51"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -2030,10 +2087,10 @@
       <c r="D9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="52" t="s">
+      <c r="E9" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="53"/>
+      <c r="F9" s="49"/>
       <c r="G9" s="5" t="s">
         <v>17</v>
       </c>
@@ -2055,18 +2112,18 @@
       <c r="M9" s="6"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A10" s="54"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="56"/>
+      <c r="A10" s="50"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="52"/>
       <c r="M10" s="2"/>
     </row>
     <row r="11" spans="1:13" ht="36" x14ac:dyDescent="0.4">
@@ -2082,10 +2139,10 @@
       <c r="D11" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="E11" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="42"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="7" t="s">
         <v>28</v>
       </c>
@@ -2119,10 +2176,10 @@
       <c r="D12" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="42"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="7" t="s">
         <v>28</v>
       </c>
@@ -2144,18 +2201,18 @@
       <c r="M12" s="2"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
-      <c r="J13" s="44"/>
-      <c r="K13" s="44"/>
-      <c r="L13" s="45"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="54"/>
+      <c r="K13" s="54"/>
+      <c r="L13" s="55"/>
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -2171,10 +2228,10 @@
       <c r="D14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="41" t="s">
+      <c r="E14" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="42"/>
+      <c r="F14" s="44"/>
       <c r="G14" s="7" t="s">
         <v>28</v>
       </c>
@@ -2208,10 +2265,10 @@
       <c r="D15" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="42"/>
+      <c r="F15" s="44"/>
       <c r="G15" s="7" t="s">
         <v>28</v>
       </c>
@@ -2245,10 +2302,10 @@
       <c r="D16" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="41" t="s">
+      <c r="E16" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="42"/>
+      <c r="F16" s="44"/>
       <c r="G16" s="7" t="s">
         <v>28</v>
       </c>
@@ -2297,10 +2354,10 @@
       <c r="D18" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="E18" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="42"/>
+      <c r="F18" s="44"/>
       <c r="G18" s="7" t="s">
         <v>28</v>
       </c>
@@ -2334,10 +2391,10 @@
       <c r="D19" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="41" t="s">
+      <c r="E19" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="42"/>
+      <c r="F19" s="44"/>
       <c r="G19" s="7" t="s">
         <v>64</v>
       </c>
@@ -2371,10 +2428,10 @@
       <c r="D20" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="42"/>
+      <c r="F20" s="44"/>
       <c r="G20" s="7" t="s">
         <v>71</v>
       </c>
@@ -2423,10 +2480,10 @@
       <c r="D22" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="E22" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="F22" s="42"/>
+      <c r="F22" s="44"/>
       <c r="G22" s="7" t="s">
         <v>28</v>
       </c>
@@ -2460,10 +2517,10 @@
       <c r="D23" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="42"/>
+      <c r="F23" s="44"/>
       <c r="G23" s="7" t="s">
         <v>84</v>
       </c>
@@ -2497,10 +2554,10 @@
       <c r="D24" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="F24" s="42"/>
+      <c r="F24" s="44"/>
       <c r="G24" s="7" t="s">
         <v>90</v>
       </c>
@@ -2534,10 +2591,10 @@
       <c r="D25" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="41" t="s">
+      <c r="E25" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="42"/>
+      <c r="F25" s="44"/>
       <c r="G25" s="7" t="s">
         <v>96</v>
       </c>
@@ -2558,7 +2615,7 @@
       </c>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="1:13" ht="107" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:13" ht="116" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="7" t="s">
         <v>101</v>
       </c>
@@ -2566,36 +2623,36 @@
         <v>75</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" s="42"/>
-      <c r="G26" s="23" t="s">
-        <v>103</v>
+        <v>344</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>345</v>
+      </c>
+      <c r="F26" s="44"/>
+      <c r="G26" s="7" t="s">
+        <v>346</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>104</v>
+        <v>347</v>
       </c>
       <c r="I26" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>28</v>
+        <v>348</v>
+      </c>
+      <c r="J26" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="K26" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="L26" s="22" t="s">
+        <v>349</v>
       </c>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="1:13" ht="218" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:13" ht="107" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="7" t="s">
         <v>106</v>
       </c>
@@ -2603,97 +2660,97 @@
         <v>75</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="E27" s="48" t="s">
-        <v>323</v>
-      </c>
-      <c r="F27" s="49"/>
+        <v>41</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" s="44"/>
       <c r="G27" s="23" t="s">
-        <v>324</v>
+        <v>103</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>328</v>
+        <v>104</v>
       </c>
       <c r="I27" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="J27" s="36" t="s">
-        <v>326</v>
-      </c>
-      <c r="K27" s="36" t="s">
-        <v>327</v>
-      </c>
-      <c r="L27" s="36" t="s">
-        <v>327</v>
+        <v>105</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="1:13" ht="282" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:13" ht="218" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="7" t="s">
         <v>112</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>329</v>
+        <v>75</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="E28" s="48" t="s">
-        <v>332</v>
-      </c>
-      <c r="F28" s="49"/>
+        <v>322</v>
+      </c>
+      <c r="E28" s="57" t="s">
+        <v>323</v>
+      </c>
+      <c r="F28" s="59"/>
       <c r="G28" s="23" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>28</v>
+        <v>325</v>
+      </c>
+      <c r="J28" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="K28" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="L28" s="36" t="s">
+        <v>327</v>
       </c>
       <c r="M28" s="2"/>
     </row>
-    <row r="29" spans="1:13" ht="90" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:13" ht="282" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="7" t="s">
         <v>118</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>75</v>
+        <v>329</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>107</v>
+        <v>330</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="7" t="s">
-        <v>109</v>
+        <v>331</v>
+      </c>
+      <c r="E29" s="57" t="s">
+        <v>332</v>
+      </c>
+      <c r="F29" s="59"/>
+      <c r="G29" s="23" t="s">
+        <v>333</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>110</v>
+        <v>334</v>
       </c>
       <c r="I29" s="12" t="s">
-        <v>111</v>
+        <v>335</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>31</v>
@@ -2706,31 +2763,31 @@
       </c>
       <c r="M29" s="2"/>
     </row>
-    <row r="30" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:13" ht="90" x14ac:dyDescent="0.4">
       <c r="A30" s="7" t="s">
         <v>125</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="17" t="s">
-        <v>113</v>
+      <c r="C30" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="F30" s="39"/>
+        <v>41</v>
+      </c>
+      <c r="E30" s="58" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="58"/>
       <c r="G30" s="7" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="I30" s="12" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>31</v>
@@ -2750,24 +2807,24 @@
       <c r="B31" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="F31" s="39"/>
+      <c r="C31" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="E31" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="F31" s="58"/>
       <c r="G31" s="7" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="I31" s="24" t="s">
-        <v>124</v>
+        <v>116</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>31</v>
@@ -2780,96 +2837,96 @@
       </c>
       <c r="M31" s="2"/>
     </row>
-    <row r="32" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A32" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="E32" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="F32" s="58"/>
+      <c r="G32" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A33" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D33" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="E32" s="47" t="s">
+      <c r="E33" s="56" t="s">
         <v>127</v>
       </c>
-      <c r="F32" s="47"/>
-      <c r="G32" s="25" t="s">
+      <c r="F33" s="56"/>
+      <c r="G33" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="H32" s="29" t="s">
+      <c r="H33" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="I32" s="30" t="s">
+      <c r="I33" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="J32" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="K32" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="L32" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="M32" s="2"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A33" s="43"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
-      <c r="J33" s="44"/>
-      <c r="K33" s="44"/>
-      <c r="L33" s="45"/>
+      <c r="J33" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" s="31" t="s">
+        <v>28</v>
+      </c>
       <c r="M33" s="2"/>
     </row>
-    <row r="34" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A34" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="E34" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="39"/>
-      <c r="G34" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="I34" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K34" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L34" s="13" t="s">
-        <v>28</v>
-      </c>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A34" s="53"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="54"/>
+      <c r="E34" s="54"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="54"/>
+      <c r="H34" s="54"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="54"/>
+      <c r="K34" s="54"/>
+      <c r="L34" s="55"/>
       <c r="M34" s="2"/>
     </row>
-    <row r="35" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A35" s="7" t="s">
         <v>147</v>
       </c>
@@ -2877,23 +2934,23 @@
         <v>132</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="F35" s="39"/>
+      <c r="F35" s="58"/>
       <c r="G35" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="I35" s="12" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="J35" s="13" t="s">
         <v>31</v>
@@ -2914,23 +2971,23 @@
         <v>132</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E36" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="39"/>
+      <c r="F36" s="58"/>
       <c r="G36" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>146</v>
+        <v>140</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>141</v>
       </c>
       <c r="J36" s="13" t="s">
         <v>31</v>
@@ -2951,23 +3008,23 @@
         <v>132</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E37" s="39" t="s">
+      <c r="E37" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="39"/>
+      <c r="F37" s="58"/>
       <c r="G37" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="I37" s="12" t="s">
-        <v>150</v>
+        <v>145</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>146</v>
       </c>
       <c r="J37" s="13" t="s">
         <v>31</v>
@@ -2980,7 +3037,7 @@
       </c>
       <c r="M37" s="2"/>
     </row>
-    <row r="38" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A38" s="7" t="s">
         <v>159</v>
       </c>
@@ -2988,23 +3045,23 @@
         <v>132</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="D38" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E38" s="39" t="s">
+      <c r="E38" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="39"/>
+      <c r="F38" s="58"/>
       <c r="G38" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I38" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J38" s="13" t="s">
         <v>31</v>
@@ -3017,7 +3074,7 @@
       </c>
       <c r="M38" s="2"/>
     </row>
-    <row r="39" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A39" s="7" t="s">
         <v>163</v>
       </c>
@@ -3025,23 +3082,23 @@
         <v>132</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D39" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E39" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="F39" s="39"/>
+      <c r="E39" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="58"/>
       <c r="G39" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I39" s="12" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="J39" s="13" t="s">
         <v>31</v>
@@ -3062,23 +3119,23 @@
         <v>132</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>160</v>
+        <v>113</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E40" s="39" t="s">
+      <c r="E40" s="58" t="s">
         <v>156</v>
       </c>
-      <c r="F40" s="39"/>
+      <c r="F40" s="58"/>
       <c r="G40" s="7" t="s">
         <v>28</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="I40" s="12" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="J40" s="13" t="s">
         <v>31</v>
@@ -3091,7 +3148,7 @@
       </c>
       <c r="M40" s="2"/>
     </row>
-    <row r="41" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A41" s="7" t="s">
         <v>172</v>
       </c>
@@ -3099,23 +3156,23 @@
         <v>132</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D41" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="F41" s="39"/>
+      <c r="E41" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="F41" s="58"/>
       <c r="G41" s="7" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="I41" s="12" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J41" s="13" t="s">
         <v>31</v>
@@ -3136,23 +3193,23 @@
         <v>132</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D42" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D42" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E42" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="39"/>
+      <c r="E42" s="58" t="s">
+        <v>165</v>
+      </c>
+      <c r="F42" s="58"/>
       <c r="G42" s="7" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="I42" s="24" t="s">
-        <v>171</v>
+        <v>166</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>167</v>
       </c>
       <c r="J42" s="13" t="s">
         <v>31</v>
@@ -3165,7 +3222,7 @@
       </c>
       <c r="M42" s="2"/>
     </row>
-    <row r="43" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A43" s="7" t="s">
         <v>183</v>
       </c>
@@ -3173,88 +3230,88 @@
         <v>132</v>
       </c>
       <c r="C43" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E43" s="58" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="58"/>
+      <c r="G43" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="I43" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L43" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M43" s="2"/>
+    </row>
+    <row r="44" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+      <c r="A44" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D44" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="E43" s="39" t="s">
+      <c r="E44" s="58" t="s">
         <v>42</v>
       </c>
-      <c r="F43" s="39"/>
-      <c r="G43" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H43" s="11" t="s">
+      <c r="F44" s="58"/>
+      <c r="G44" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H44" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="I43" s="12" t="s">
+      <c r="I44" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="J43" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K43" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L43" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M43" s="2"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A44" s="43"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-      <c r="I44" s="44"/>
-      <c r="J44" s="44"/>
-      <c r="K44" s="44"/>
-      <c r="L44" s="45"/>
+      <c r="J44" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L44" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="M44" s="2"/>
     </row>
-    <row r="45" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A45" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E45" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="F45" s="39"/>
-      <c r="G45" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="I45" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K45" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L45" s="13" t="s">
-        <v>28</v>
-      </c>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A45" s="53"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="54"/>
+      <c r="F45" s="54"/>
+      <c r="G45" s="54"/>
+      <c r="H45" s="54"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="54"/>
+      <c r="L45" s="55"/>
       <c r="M45" s="2"/>
     </row>
-    <row r="46" spans="1:13" ht="147" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A46" s="7" t="s">
         <v>196</v>
       </c>
@@ -3262,36 +3319,36 @@
         <v>177</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E46" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="F46" s="39"/>
+      <c r="E46" s="58" t="s">
+        <v>179</v>
+      </c>
+      <c r="F46" s="58"/>
       <c r="G46" s="7" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I46" s="12" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="J46" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K46" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="L46" s="32" t="s">
-        <v>189</v>
+      <c r="K46" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L46" s="13" t="s">
+        <v>28</v>
       </c>
       <c r="M46" s="2"/>
     </row>
-    <row r="47" spans="1:13" ht="159" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:13" ht="147" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="7" t="s">
         <v>201</v>
       </c>
@@ -3299,23 +3356,23 @@
         <v>177</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E47" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="F47" s="39"/>
+      <c r="E47" s="58" t="s">
+        <v>185</v>
+      </c>
+      <c r="F47" s="58"/>
       <c r="G47" s="7" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="I47" s="12" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="J47" s="13" t="s">
         <v>31</v>
@@ -3328,93 +3385,93 @@
       </c>
       <c r="M47" s="2"/>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A48" s="43"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
+    <row r="48" spans="1:13" ht="147" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E48" s="43" t="s">
+        <v>351</v>
+      </c>
       <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="44"/>
-      <c r="L48" s="45"/>
+      <c r="G48" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="J48" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="K48" s="63" t="s">
+        <v>327</v>
+      </c>
+      <c r="L48" s="63" t="s">
+        <v>355</v>
+      </c>
       <c r="M48" s="2"/>
     </row>
-    <row r="49" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:13" ht="159" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E49" s="39" t="s">
-        <v>199</v>
-      </c>
-      <c r="F49" s="39"/>
+      <c r="E49" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="F49" s="58"/>
       <c r="G49" s="7" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="I49" s="12" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="J49" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="K49" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L49" s="13" t="s">
-        <v>28</v>
+      <c r="K49" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L49" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="M49" s="2"/>
     </row>
-    <row r="50" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A50" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="E50" s="39" t="s">
-        <v>203</v>
-      </c>
-      <c r="F50" s="39"/>
-      <c r="G50" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="I50" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="J50" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K50" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L50" s="13" t="s">
-        <v>28</v>
-      </c>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A50" s="53"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="54"/>
+      <c r="I50" s="54"/>
+      <c r="J50" s="54"/>
+      <c r="K50" s="54"/>
+      <c r="L50" s="55"/>
       <c r="M50" s="2"/>
     </row>
     <row r="51" spans="1:13" ht="54" x14ac:dyDescent="0.4">
@@ -3425,113 +3482,135 @@
         <v>197</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="E51" s="39" t="s">
+      <c r="E51" s="58" t="s">
+        <v>199</v>
+      </c>
+      <c r="F51" s="58"/>
+      <c r="G51" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K51" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L51" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A52" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E52" s="58" t="s">
+        <v>203</v>
+      </c>
+      <c r="F52" s="58"/>
+      <c r="G52" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="I52" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L52" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M52" s="2"/>
+    </row>
+    <row r="53" spans="1:13" ht="152.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" s="43" t="s">
+        <v>356</v>
+      </c>
+      <c r="F53" s="44"/>
+      <c r="G53" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="J53" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="K53" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="L53" s="36" t="s">
+        <v>355</v>
+      </c>
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A54" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="E54" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="F51" s="39"/>
-      <c r="G51" s="7" t="s">
+      <c r="F54" s="58"/>
+      <c r="G54" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H54" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="I51" s="12" t="s">
+      <c r="I54" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="J51" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K51" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L51" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M51" s="2"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A52" s="43"/>
-      <c r="B52" s="44"/>
-      <c r="C52" s="44"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="44"/>
-      <c r="G52" s="44"/>
-      <c r="H52" s="44"/>
-      <c r="I52" s="44"/>
-      <c r="J52" s="44"/>
-      <c r="K52" s="44"/>
-      <c r="L52" s="45"/>
-      <c r="M52" s="2"/>
-    </row>
-    <row r="53" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A53" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E53" s="41" t="s">
-        <v>212</v>
-      </c>
-      <c r="F53" s="42"/>
-      <c r="G53" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="I53" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="J53" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K53" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L53" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M53" s="2"/>
-    </row>
-    <row r="54" spans="1:13" ht="36" x14ac:dyDescent="0.4">
-      <c r="A54" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E54" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="F54" s="42"/>
-      <c r="G54" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="I54" s="12" t="s">
-        <v>219</v>
-      </c>
       <c r="J54" s="13" t="s">
         <v>31</v>
       </c>
@@ -3543,44 +3622,22 @@
       </c>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A55" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E55" s="41" t="s">
-        <v>222</v>
-      </c>
-      <c r="F55" s="42"/>
-      <c r="G55" s="7">
-        <v>9988776655</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="I55" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="J55" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K55" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L55" s="13" t="s">
-        <v>28</v>
-      </c>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A55" s="53"/>
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="54"/>
+      <c r="H55" s="54"/>
+      <c r="I55" s="54"/>
+      <c r="J55" s="54"/>
+      <c r="K55" s="54"/>
+      <c r="L55" s="55"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A56" s="7" t="s">
         <v>234</v>
       </c>
@@ -3588,23 +3645,23 @@
         <v>209</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="D56" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E56" s="41" t="s">
-        <v>227</v>
-      </c>
-      <c r="F56" s="42"/>
-      <c r="G56" s="7">
-        <v>998877665</v>
+      <c r="E56" s="43" t="s">
+        <v>212</v>
+      </c>
+      <c r="F56" s="44"/>
+      <c r="G56" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J56" s="13" t="s">
         <v>31</v>
@@ -3617,7 +3674,7 @@
       </c>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A57" s="7" t="s">
         <v>240</v>
       </c>
@@ -3625,23 +3682,23 @@
         <v>209</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E57" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="F57" s="42"/>
-      <c r="G57" s="7">
-        <v>99887766554</v>
+      <c r="E57" s="43" t="s">
+        <v>217</v>
+      </c>
+      <c r="F57" s="44"/>
+      <c r="G57" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="J57" s="13" t="s">
         <v>31</v>
@@ -3662,23 +3719,23 @@
         <v>209</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E58" s="41" t="s">
-        <v>236</v>
-      </c>
-      <c r="F58" s="42"/>
-      <c r="G58" s="7" t="s">
-        <v>237</v>
+      <c r="E58" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="F58" s="44"/>
+      <c r="G58" s="7">
+        <v>9988776655</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="I58" s="12" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="J58" s="13" t="s">
         <v>31</v>
@@ -3691,46 +3748,68 @@
       </c>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A59" s="43"/>
-      <c r="B59" s="44"/>
-      <c r="C59" s="44"/>
-      <c r="D59" s="44"/>
-      <c r="E59" s="44"/>
+    <row r="59" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+      <c r="A59" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E59" s="43" t="s">
+        <v>227</v>
+      </c>
       <c r="F59" s="44"/>
-      <c r="G59" s="44"/>
-      <c r="H59" s="44"/>
-      <c r="I59" s="44"/>
-      <c r="J59" s="44"/>
-      <c r="K59" s="44"/>
-      <c r="L59" s="45"/>
+      <c r="G59" s="7">
+        <v>998877665</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K59" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L59" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A60" s="7" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E60" s="41" t="s">
-        <v>243</v>
-      </c>
-      <c r="F60" s="42"/>
-      <c r="G60" s="7" t="s">
-        <v>28</v>
+      <c r="E60" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="F60" s="44"/>
+      <c r="G60" s="7">
+        <v>99887766554</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="J60" s="13" t="s">
         <v>31</v>
@@ -3743,31 +3822,31 @@
       </c>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A61" s="7" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E61" s="41" t="s">
-        <v>248</v>
-      </c>
-      <c r="F61" s="42"/>
+      <c r="E61" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="F61" s="44"/>
       <c r="G61" s="7" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="J61" s="13" t="s">
         <v>31</v>
@@ -3780,44 +3859,22 @@
       </c>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A62" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E62" s="41" t="s">
-        <v>254</v>
-      </c>
-      <c r="F62" s="42"/>
-      <c r="G62" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="H62" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="I62" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="J62" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K62" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L62" s="13" t="s">
-        <v>28</v>
-      </c>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A62" s="53"/>
+      <c r="B62" s="54"/>
+      <c r="C62" s="54"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="54"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="54"/>
+      <c r="H62" s="54"/>
+      <c r="I62" s="54"/>
+      <c r="J62" s="54"/>
+      <c r="K62" s="54"/>
+      <c r="L62" s="55"/>
       <c r="M62" s="2"/>
     </row>
-    <row r="63" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:13" ht="72" x14ac:dyDescent="0.4">
       <c r="A63" s="7" t="s">
         <v>269</v>
       </c>
@@ -3825,23 +3882,23 @@
         <v>241</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E63" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="F63" s="42"/>
+      <c r="E63" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="F63" s="44"/>
       <c r="G63" s="7" t="s">
-        <v>260</v>
+        <v>28</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="J63" s="13" t="s">
         <v>31</v>
@@ -3854,7 +3911,7 @@
       </c>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A64" s="7" t="s">
         <v>274</v>
       </c>
@@ -3862,23 +3919,23 @@
         <v>241</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E64" s="41" t="s">
-        <v>265</v>
-      </c>
-      <c r="F64" s="42"/>
+      <c r="E64" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="F64" s="44"/>
       <c r="G64" s="7" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="I64" s="12" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="J64" s="13" t="s">
         <v>31</v>
@@ -3891,46 +3948,68 @@
       </c>
       <c r="M64" s="2"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A65" s="43"/>
-      <c r="B65" s="44"/>
-      <c r="C65" s="44"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
+    <row r="65" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A65" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E65" s="43" t="s">
+        <v>254</v>
+      </c>
       <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="44"/>
-      <c r="K65" s="44"/>
-      <c r="L65" s="45"/>
+      <c r="G65" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="J65" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K65" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L65" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="M65" s="2"/>
     </row>
-    <row r="66" spans="1:13" ht="90" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A66" s="7" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E66" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="F66" s="42"/>
+      <c r="E66" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="F66" s="44"/>
       <c r="G66" s="7" t="s">
-        <v>28</v>
+        <v>260</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="J66" s="13" t="s">
         <v>31</v>
@@ -3943,31 +4022,31 @@
       </c>
       <c r="M66" s="2"/>
     </row>
-    <row r="67" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:13" ht="72" x14ac:dyDescent="0.4">
       <c r="A67" s="7" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E67" s="41" t="s">
-        <v>276</v>
-      </c>
-      <c r="F67" s="42"/>
+      <c r="E67" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="F67" s="44"/>
       <c r="G67" s="7" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="J67" s="13" t="s">
         <v>31</v>
@@ -3980,44 +4059,22 @@
       </c>
       <c r="M67" s="2"/>
     </row>
-    <row r="68" spans="1:13" ht="54" x14ac:dyDescent="0.4">
-      <c r="A68" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>270</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E68" s="41" t="s">
-        <v>281</v>
-      </c>
-      <c r="F68" s="42"/>
-      <c r="G68" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="H68" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="I68" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="J68" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K68" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L68" s="13" t="s">
-        <v>28</v>
-      </c>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A68" s="53"/>
+      <c r="B68" s="54"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="54"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="54"/>
+      <c r="I68" s="54"/>
+      <c r="J68" s="54"/>
+      <c r="K68" s="54"/>
+      <c r="L68" s="55"/>
       <c r="M68" s="2"/>
     </row>
-    <row r="69" spans="1:13" ht="36" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:13" ht="90" x14ac:dyDescent="0.4">
       <c r="A69" s="7" t="s">
         <v>295</v>
       </c>
@@ -4025,23 +4082,23 @@
         <v>270</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="D69" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E69" s="41" t="s">
-        <v>286</v>
-      </c>
-      <c r="F69" s="42"/>
+      <c r="E69" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="F69" s="44"/>
       <c r="G69" s="7" t="s">
-        <v>277</v>
+        <v>28</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="I69" s="12" t="s">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="J69" s="13" t="s">
         <v>31</v>
@@ -4062,23 +4119,23 @@
         <v>270</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="D70" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E70" s="41" t="s">
-        <v>291</v>
-      </c>
-      <c r="F70" s="42"/>
+      <c r="E70" s="43" t="s">
+        <v>276</v>
+      </c>
+      <c r="F70" s="44"/>
       <c r="G70" s="7" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="I70" s="12" t="s">
-        <v>294</v>
+        <v>251</v>
       </c>
       <c r="J70" s="13" t="s">
         <v>31</v>
@@ -4091,46 +4148,68 @@
       </c>
       <c r="M70" s="2"/>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A71" s="43"/>
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
+    <row r="71" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A71" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E71" s="43" t="s">
+        <v>281</v>
+      </c>
       <c r="F71" s="44"/>
-      <c r="G71" s="44"/>
-      <c r="H71" s="44"/>
-      <c r="I71" s="44"/>
-      <c r="J71" s="44"/>
-      <c r="K71" s="44"/>
-      <c r="L71" s="45"/>
+      <c r="G71" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K71" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L71" s="13" t="s">
+        <v>28</v>
+      </c>
       <c r="M71" s="2"/>
     </row>
-    <row r="72" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.4">
       <c r="A72" s="7" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D72" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E72" s="41" t="s">
-        <v>298</v>
-      </c>
-      <c r="F72" s="42"/>
+      <c r="E72" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="F72" s="44"/>
       <c r="G72" s="7" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="I72" s="12" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="J72" s="13" t="s">
         <v>31</v>
@@ -4145,29 +4224,29 @@
     </row>
     <row r="73" spans="1:13" ht="54" x14ac:dyDescent="0.4">
       <c r="A73" s="7" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="C73" s="17" t="s">
-        <v>303</v>
+        <v>270</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>290</v>
       </c>
       <c r="D73" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E73" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="F73" s="42"/>
+      <c r="E73" s="43" t="s">
+        <v>291</v>
+      </c>
+      <c r="F73" s="44"/>
       <c r="G73" s="7" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="I73" s="12" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="J73" s="13" t="s">
         <v>31</v>
@@ -4180,41 +4259,19 @@
       </c>
       <c r="M73" s="2"/>
     </row>
-    <row r="74" spans="1:13" ht="72" x14ac:dyDescent="0.4">
-      <c r="A74" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="E74" s="41" t="s">
-        <v>310</v>
-      </c>
-      <c r="F74" s="42"/>
-      <c r="G74" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="H74" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="I74" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="J74" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K74" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L74" s="13" t="s">
-        <v>28</v>
-      </c>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A74" s="53"/>
+      <c r="B74" s="54"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="54"/>
+      <c r="H74" s="54"/>
+      <c r="I74" s="54"/>
+      <c r="J74" s="54"/>
+      <c r="K74" s="54"/>
+      <c r="L74" s="55"/>
       <c r="M74" s="2"/>
     </row>
     <row r="75" spans="1:13" ht="72" x14ac:dyDescent="0.4">
@@ -4225,98 +4282,160 @@
         <v>296</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="E75" s="39" t="s">
+      <c r="E75" s="43" t="s">
+        <v>298</v>
+      </c>
+      <c r="F75" s="44"/>
+      <c r="G75" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="H75" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>301</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L75" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M75" s="2"/>
+    </row>
+    <row r="76" spans="1:13" ht="54" x14ac:dyDescent="0.4">
+      <c r="A76" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" s="43" t="s">
+        <v>304</v>
+      </c>
+      <c r="F76" s="44"/>
+      <c r="G76" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="H76" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K76" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L76" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M76" s="2"/>
+    </row>
+    <row r="77" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+      <c r="A77" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E77" s="43" t="s">
+        <v>310</v>
+      </c>
+      <c r="F77" s="44"/>
+      <c r="G77" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H77" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K77" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L77" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M77" s="2"/>
+    </row>
+    <row r="78" spans="1:13" ht="72" x14ac:dyDescent="0.4">
+      <c r="A78" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="E78" s="58" t="s">
         <v>314</v>
       </c>
-      <c r="F75" s="39"/>
-      <c r="G75" s="7" t="s">
+      <c r="F78" s="58"/>
+      <c r="G78" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H78" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="I75" s="12" t="s">
+      <c r="I78" s="12" t="s">
         <v>316</v>
       </c>
-      <c r="J75" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="K75" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="L75" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="M75" s="2"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="40"/>
-      <c r="L76" s="40"/>
-      <c r="M76" s="2"/>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="37" t="s">
-        <v>337</v>
-      </c>
-      <c r="J77" s="37"/>
-      <c r="K77" s="37"/>
-      <c r="L77" s="37"/>
-      <c r="M77" s="34"/>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="46" t="s">
-        <v>317</v>
-      </c>
-      <c r="J78" s="46"/>
-      <c r="K78" s="46"/>
-      <c r="L78" s="46"/>
-      <c r="M78" s="34"/>
+      <c r="J78" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="K78" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L78" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M78" s="2"/>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.4">
-      <c r="A79" s="33"/>
-      <c r="B79" s="33"/>
-      <c r="C79" s="33"/>
-      <c r="D79" s="33"/>
-      <c r="E79" s="33"/>
-      <c r="F79" s="33"/>
-      <c r="G79" s="33"/>
-      <c r="H79" s="33"/>
-      <c r="I79" s="38"/>
-      <c r="J79" s="38"/>
-      <c r="K79" s="38"/>
-      <c r="L79" s="38"/>
-      <c r="M79" s="35"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
+      <c r="C79" s="4"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="4"/>
+      <c r="H79" s="4"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="45"/>
+      <c r="L79" s="45"/>
+      <c r="M79" s="2"/>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A80" s="4"/>
@@ -4327,10 +4446,15 @@
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
       <c r="H80" s="4"/>
-      <c r="I80" s="4"/>
-      <c r="J80" s="4"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="I80" s="60" t="s">
+        <v>337</v>
+      </c>
+      <c r="J80" s="60"/>
+      <c r="K80" s="60"/>
+      <c r="L80" s="60"/>
+      <c r="M80" s="34"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -4339,22 +4463,30 @@
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
       <c r="H81" s="4"/>
-      <c r="I81" s="4"/>
-      <c r="J81" s="4"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="4"/>
-      <c r="J82" s="4"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="I81" s="62" t="s">
+        <v>317</v>
+      </c>
+      <c r="J81" s="62"/>
+      <c r="K81" s="62"/>
+      <c r="L81" s="62"/>
+      <c r="M81" s="34"/>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A82" s="33"/>
+      <c r="B82" s="33"/>
+      <c r="C82" s="33"/>
+      <c r="D82" s="33"/>
+      <c r="E82" s="33"/>
+      <c r="F82" s="33"/>
+      <c r="G82" s="33"/>
+      <c r="H82" s="33"/>
+      <c r="I82" s="61"/>
+      <c r="J82" s="61"/>
+      <c r="K82" s="61"/>
+      <c r="L82" s="61"/>
+      <c r="M82" s="35"/>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -4366,24 +4498,108 @@
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
     </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="4"/>
+      <c r="H84" s="4"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="4"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
+      <c r="C86" s="4"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="4"/>
+      <c r="H86" s="4"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="89">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
+  <mergeCells count="92">
+    <mergeCell ref="I80:L80"/>
+    <mergeCell ref="I82:L82"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="A74:L74"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
+    <mergeCell ref="I81:L81"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="A62:L62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="A68:L68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="A55:L55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E6:F6"/>
@@ -4396,75 +4612,30 @@
     <mergeCell ref="A13:L13"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="A33:L33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="A52:L52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="A59:L59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="A65:L65"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="I77:L77"/>
-    <mergeCell ref="I79:L79"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="K76:L76"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="A71:L71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="I78:L78"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G29" r:id="rId1" display="sanjay@gmail&quot;" xr:uid="{20C29829-2576-487E-9721-0A3014FAB7B9}"/>
-    <hyperlink ref="G31" r:id="rId2" xr:uid="{D21CDC16-49F6-4309-96A9-2E51498E21C8}"/>
-    <hyperlink ref="G32" r:id="rId3" xr:uid="{E8D07DF6-8D59-44A0-9572-73626C8E4D0B}"/>
-    <hyperlink ref="G41" r:id="rId4" xr:uid="{DC0EB2BA-84FD-4926-A351-EE2D56BE34B2}"/>
-    <hyperlink ref="G61" r:id="rId5" xr:uid="{657EF47E-91F6-44AC-8CC5-5DBD1BCD4B49}"/>
+    <hyperlink ref="G30" r:id="rId1" display="sanjay@gmail&quot;" xr:uid="{20C29829-2576-487E-9721-0A3014FAB7B9}"/>
+    <hyperlink ref="G32" r:id="rId2" xr:uid="{D21CDC16-49F6-4309-96A9-2E51498E21C8}"/>
+    <hyperlink ref="G33" r:id="rId3" xr:uid="{E8D07DF6-8D59-44A0-9572-73626C8E4D0B}"/>
+    <hyperlink ref="G42" r:id="rId4" xr:uid="{DC0EB2BA-84FD-4926-A351-EE2D56BE34B2}"/>
+    <hyperlink ref="G64" r:id="rId5" xr:uid="{657EF47E-91F6-44AC-8CC5-5DBD1BCD4B49}"/>
     <hyperlink ref="C3" r:id="rId6" xr:uid="{3EEF9359-C10C-4BC6-8CE6-AE96837A9394}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
